--- a/docs/GE2ExcelTestFile.xlsx
+++ b/docs/GE2ExcelTestFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanmichaelnuera/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{152DA7F2-75F7-1844-B957-5FA5FF57C46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D2458DE-DF1A-BD46-98EC-21649627E189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="552">
   <si>
     <t>VARIABLE</t>
   </si>
@@ -796,9 +796,6 @@
     <t>test1.json</t>
   </si>
   <si>
-    <t>SHA-256 string (valid)</t>
-  </si>
-  <si>
     <t>testcase_2</t>
   </si>
   <si>
@@ -1739,6 +1736,18 @@
   </si>
   <si>
     <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>Input file not found.</t>
+  </si>
+  <si>
+    <t>994da7c4d18c65f0dfc5715848fe132556d0f80e705a0e8d620c79939de29e31</t>
+  </si>
+  <si>
+    <t>0abec6611f29374af22889bec468e450657aaa9832886a449fe2d4f937d23295</t>
+  </si>
+  <si>
+    <t>1339927c516401a3dfe3ca7720347c9a4db73f4a20c086ecd315446e6483575e</t>
   </si>
 </sst>
 </file>
@@ -8071,7 +8080,7 @@
     <col min="6" max="6" width="28.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="59" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="9" max="9" width="57.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="10.42578125" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -8152,10 +8161,10 @@
         <v>233</v>
       </c>
       <c r="H2" s="64" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I2" s="65" t="s">
-        <v>234</v>
+        <v>549</v>
       </c>
       <c r="J2" s="62"/>
       <c r="O2" s="47"/>
@@ -8174,19 +8183,19 @@
         <v>230</v>
       </c>
       <c r="E3" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="F3" s="66" t="s">
         <v>235</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="G3" s="65" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="65" t="s">
-        <v>237</v>
-      </c>
       <c r="H3" s="64" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I3" s="65" t="s">
-        <v>234</v>
+        <v>550</v>
       </c>
       <c r="J3" s="62"/>
       <c r="O3" s="47"/>
@@ -8208,19 +8217,19 @@
         <v>230</v>
       </c>
       <c r="E4" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="F4" s="66" t="s">
+      <c r="G4" s="65" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="65" t="s">
-        <v>240</v>
-      </c>
       <c r="H4" s="64" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I4" s="65" t="s">
-        <v>234</v>
+        <v>551</v>
       </c>
       <c r="J4" s="62"/>
       <c r="O4" s="47"/>
@@ -8233,23 +8242,23 @@
         <v>1</v>
       </c>
       <c r="C5" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="E5" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="F5" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="G5" s="65" t="s">
         <v>244</v>
-      </c>
-      <c r="G5" s="65" t="s">
-        <v>245</v>
       </c>
       <c r="H5" s="65"/>
       <c r="I5" s="30" t="s">
-        <v>140</v>
+        <v>548</v>
       </c>
       <c r="J5" s="62"/>
       <c r="O5" s="47"/>
@@ -8262,22 +8271,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D6" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="F6" s="64" t="s">
         <v>247</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="G6" s="65" t="s">
         <v>248</v>
       </c>
-      <c r="G6" s="65" t="s">
-        <v>249</v>
-      </c>
       <c r="H6" s="66" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>140</v>
@@ -8290,25 +8299,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="D7" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="D7" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E7" s="51" t="s">
+      <c r="F7" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="G7" s="65" t="s">
         <v>253</v>
       </c>
-      <c r="G7" s="65" t="s">
-        <v>254</v>
-      </c>
       <c r="H7" s="66" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>140</v>
@@ -8321,25 +8330,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="51" t="s">
-        <v>251</v>
-      </c>
       <c r="D8" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E8" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="F8" s="64" t="s">
+      <c r="G8" s="65" t="s">
         <v>256</v>
       </c>
-      <c r="G8" s="65" t="s">
-        <v>257</v>
-      </c>
       <c r="H8" s="66" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I8" s="30" t="s">
         <v>140</v>
@@ -8354,22 +8363,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D9" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="E9" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="F9" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="G9" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="G9" s="51" t="s">
-        <v>262</v>
-      </c>
       <c r="H9" s="66" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I9" s="30" t="s">
         <v>140</v>
@@ -8384,22 +8393,22 @@
         <v>3</v>
       </c>
       <c r="C10" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E10" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="64" t="s">
         <v>263</v>
       </c>
-      <c r="F10" s="64" t="s">
+      <c r="G10" s="65" t="s">
         <v>264</v>
       </c>
-      <c r="G10" s="65" t="s">
+      <c r="H10" s="51" t="s">
         <v>265</v>
-      </c>
-      <c r="H10" s="51" t="s">
-        <v>266</v>
       </c>
       <c r="I10" s="30" t="s">
         <v>140</v>
@@ -8414,22 +8423,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E11" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="64" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="G11" s="65" t="s">
         <v>268</v>
       </c>
-      <c r="G11" s="65" t="s">
-        <v>269</v>
-      </c>
       <c r="H11" s="64" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>140</v>
@@ -8441,25 +8450,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="51" t="s">
+      <c r="F12" s="64" t="s">
         <v>271</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="G12" s="65" t="s">
         <v>272</v>
       </c>
-      <c r="G12" s="65" t="s">
-        <v>273</v>
-      </c>
       <c r="H12" s="64" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I12" s="30" t="s">
         <v>140</v>
@@ -8471,25 +8480,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E13" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="F13" s="64" t="s">
         <v>274</v>
       </c>
-      <c r="F13" s="64" t="s">
+      <c r="G13" s="65" t="s">
         <v>275</v>
       </c>
-      <c r="G13" s="65" t="s">
-        <v>276</v>
-      </c>
       <c r="H13" s="66" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I13" s="30" t="s">
         <v>140</v>
@@ -8504,22 +8513,22 @@
         <v>9</v>
       </c>
       <c r="C14" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D14" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E14" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="51" t="s">
         <v>277</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="G14" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="G14" s="51" t="s">
-        <v>279</v>
-      </c>
       <c r="H14" s="66" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I14" s="30" t="s">
         <v>140</v>
@@ -8534,22 +8543,22 @@
         <v>6</v>
       </c>
       <c r="C15" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D15" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E15" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="G15" s="65" t="s">
         <v>281</v>
       </c>
-      <c r="G15" s="65" t="s">
-        <v>282</v>
-      </c>
       <c r="H15" s="70" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I15" s="30" t="s">
         <v>140</v>
@@ -8564,22 +8573,22 @@
         <v>6</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E16" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" s="64" t="s">
         <v>283</v>
       </c>
-      <c r="F16" s="64" t="s">
+      <c r="G16" s="65" t="s">
         <v>284</v>
       </c>
-      <c r="G16" s="65" t="s">
-        <v>285</v>
-      </c>
       <c r="H16" s="66" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I16" s="30" t="s">
         <v>140</v>
@@ -8591,25 +8600,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="C17" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="51" t="s">
+      <c r="F17" s="64" t="s">
         <v>287</v>
       </c>
-      <c r="F17" s="64" t="s">
+      <c r="G17" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="G17" s="65" t="s">
-        <v>289</v>
-      </c>
       <c r="H17" s="66" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I17" s="30" t="s">
         <v>140</v>
@@ -8621,25 +8630,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E18" s="51" t="s">
+        <v>289</v>
+      </c>
+      <c r="F18" s="64" t="s">
         <v>290</v>
       </c>
-      <c r="F18" s="64" t="s">
+      <c r="G18" s="65" t="s">
         <v>291</v>
       </c>
-      <c r="G18" s="65" t="s">
-        <v>292</v>
-      </c>
       <c r="H18" s="66" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I18" s="30" t="s">
         <v>140</v>
@@ -8654,22 +8663,22 @@
         <v>13</v>
       </c>
       <c r="C19" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D19" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D19" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E19" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="F19" s="51" t="s">
         <v>293</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="G19" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="G19" s="51" t="s">
-        <v>295</v>
-      </c>
       <c r="H19" s="66" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I19" s="30" t="s">
         <v>140</v>
@@ -8684,22 +8693,22 @@
         <v>8</v>
       </c>
       <c r="C20" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D20" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E20" s="51" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="G20" s="65" t="s">
         <v>297</v>
       </c>
-      <c r="G20" s="65" t="s">
-        <v>298</v>
-      </c>
       <c r="H20" s="66" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I20" s="30" t="s">
         <v>140</v>
@@ -8714,22 +8723,22 @@
         <v>8</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E21" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="F21" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="G21" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="G21" s="65" t="s">
-        <v>301</v>
-      </c>
       <c r="H21" s="66" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I21" s="30" t="s">
         <v>140</v>
@@ -8744,22 +8753,22 @@
         <v>10</v>
       </c>
       <c r="C22" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D22" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E22" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="F22" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="G22" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="G22" s="65" t="s">
-        <v>304</v>
-      </c>
       <c r="H22" s="64" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I22" s="30" t="s">
         <v>140</v>
@@ -8774,22 +8783,22 @@
         <v>10</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E23" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="F23" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="G23" s="65" t="s">
         <v>306</v>
       </c>
-      <c r="G23" s="65" t="s">
-        <v>307</v>
-      </c>
       <c r="H23" s="66" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I23" s="30" t="s">
         <v>140</v>
@@ -8801,25 +8810,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="C24" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D24" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E24" s="51" t="s">
+      <c r="F24" s="64" t="s">
         <v>309</v>
       </c>
-      <c r="F24" s="64" t="s">
+      <c r="G24" s="65" t="s">
         <v>310</v>
       </c>
-      <c r="G24" s="65" t="s">
-        <v>311</v>
-      </c>
       <c r="H24" s="64" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I24" s="30" t="s">
         <v>140</v>
@@ -8831,25 +8840,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E25" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="F25" s="64" t="s">
         <v>312</v>
       </c>
-      <c r="F25" s="64" t="s">
+      <c r="G25" s="65" t="s">
         <v>313</v>
       </c>
-      <c r="G25" s="65" t="s">
-        <v>314</v>
-      </c>
       <c r="H25" s="64" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I25" s="30" t="s">
         <v>140</v>
@@ -8864,22 +8873,22 @@
         <v>20</v>
       </c>
       <c r="C26" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D26" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D26" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E26" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="F26" s="51" t="s">
         <v>315</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="G26" s="51" t="s">
         <v>316</v>
       </c>
-      <c r="G26" s="51" t="s">
-        <v>317</v>
-      </c>
       <c r="H26" s="66" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I26" s="30" t="s">
         <v>140</v>
@@ -8894,22 +8903,22 @@
         <v>12</v>
       </c>
       <c r="C27" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D27" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E27" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="F27" s="51" t="s">
         <v>318</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="G27" s="65" t="s">
         <v>319</v>
       </c>
-      <c r="G27" s="65" t="s">
-        <v>320</v>
-      </c>
       <c r="H27" s="66" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I27" s="30" t="s">
         <v>140</v>
@@ -8924,22 +8933,22 @@
         <v>12</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E28" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="F28" s="51" t="s">
         <v>321</v>
       </c>
-      <c r="F28" s="51" t="s">
+      <c r="G28" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="G28" s="51" t="s">
-        <v>323</v>
-      </c>
       <c r="H28" s="66" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I28" s="30" t="s">
         <v>140</v>
@@ -8954,22 +8963,22 @@
         <v>14</v>
       </c>
       <c r="C29" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D29" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E29" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="F29" s="51" t="s">
         <v>324</v>
       </c>
-      <c r="F29" s="51" t="s">
+      <c r="G29" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="G29" s="51" t="s">
-        <v>326</v>
-      </c>
       <c r="H29" s="66" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I29" s="30" t="s">
         <v>140</v>
@@ -8984,22 +8993,22 @@
         <v>14</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E30" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="F30" s="51" t="s">
         <v>327</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="G30" s="51" t="s">
         <v>328</v>
       </c>
-      <c r="G30" s="51" t="s">
-        <v>329</v>
-      </c>
       <c r="H30" s="64" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I30" s="30" t="s">
         <v>140</v>
@@ -9011,25 +9020,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="51" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" s="51" t="s">
         <v>330</v>
       </c>
-      <c r="C31" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E31" s="51" t="s">
+      <c r="F31" s="64" t="s">
         <v>331</v>
       </c>
-      <c r="F31" s="64" t="s">
+      <c r="G31" s="51" t="s">
         <v>332</v>
       </c>
-      <c r="G31" s="51" t="s">
-        <v>333</v>
-      </c>
       <c r="H31" s="66" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I31" s="30" t="s">
         <v>140</v>
@@ -9041,25 +9050,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E32" s="51" t="s">
+        <v>333</v>
+      </c>
+      <c r="F32" s="64" t="s">
         <v>334</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="G32" s="51" t="s">
         <v>335</v>
       </c>
-      <c r="G32" s="51" t="s">
-        <v>336</v>
-      </c>
       <c r="H32" s="64" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I32" s="30" t="s">
         <v>140</v>
@@ -9074,22 +9083,22 @@
         <v>27</v>
       </c>
       <c r="C33" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D33" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E33" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="F33" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="F33" s="64" t="s">
+      <c r="G33" s="51" t="s">
         <v>338</v>
       </c>
-      <c r="G33" s="51" t="s">
-        <v>339</v>
-      </c>
       <c r="H33" s="66" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I33" s="30" t="s">
         <v>140</v>
@@ -9104,22 +9113,22 @@
         <v>16</v>
       </c>
       <c r="C34" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D34" s="51" t="s">
-        <v>242</v>
-      </c>
       <c r="E34" s="51" t="s">
+        <v>339</v>
+      </c>
+      <c r="F34" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="G34" s="51" t="s">
         <v>341</v>
       </c>
-      <c r="G34" s="51" t="s">
-        <v>342</v>
-      </c>
       <c r="H34" s="66" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I34" s="30" t="s">
         <v>140</v>
@@ -9134,22 +9143,22 @@
         <v>16</v>
       </c>
       <c r="C35" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="D35" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="E35" s="51" t="s">
+      <c r="F35" s="51" t="s">
         <v>344</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="G35" s="51" t="s">
         <v>345</v>
       </c>
-      <c r="G35" s="51" t="s">
-        <v>346</v>
-      </c>
       <c r="H35" s="64" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I35" s="30" t="s">
         <v>140</v>
@@ -9161,25 +9170,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="51" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="51" t="s">
         <v>347</v>
       </c>
-      <c r="C36" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D36" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E36" s="51" t="s">
+      <c r="F36" s="64" t="s">
         <v>348</v>
       </c>
-      <c r="F36" s="64" t="s">
+      <c r="G36" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="G36" s="51" t="s">
-        <v>350</v>
-      </c>
       <c r="H36" s="66" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I36" s="30" t="s">
         <v>140</v>
@@ -9191,25 +9200,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E37" s="51" t="s">
+        <v>350</v>
+      </c>
+      <c r="F37" s="54" t="s">
         <v>351</v>
       </c>
-      <c r="F37" s="54" t="s">
+      <c r="G37" s="51" t="s">
         <v>352</v>
       </c>
-      <c r="G37" s="51" t="s">
-        <v>353</v>
-      </c>
       <c r="H37" s="66" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I37" s="30" t="s">
         <v>140</v>
@@ -9224,22 +9233,22 @@
         <v>31</v>
       </c>
       <c r="C38" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D38" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D38" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E38" s="51" t="s">
+        <v>353</v>
+      </c>
+      <c r="F38" s="51" t="s">
         <v>354</v>
       </c>
-      <c r="F38" s="51" t="s">
+      <c r="G38" s="51" t="s">
         <v>355</v>
       </c>
-      <c r="G38" s="51" t="s">
-        <v>356</v>
-      </c>
       <c r="H38" s="66" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I38" s="30" t="s">
         <v>140</v>
@@ -9251,25 +9260,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="51" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="C39" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E39" s="51" t="s">
+      <c r="F39" s="64" t="s">
         <v>358</v>
       </c>
-      <c r="F39" s="64" t="s">
+      <c r="G39" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="G39" s="51" t="s">
-        <v>360</v>
-      </c>
       <c r="H39" s="66" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I39" s="30" t="s">
         <v>140</v>
@@ -9281,25 +9290,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C40" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="F40" s="55" t="s">
         <v>361</v>
       </c>
-      <c r="F40" s="55" t="s">
+      <c r="G40" s="51" t="s">
         <v>362</v>
       </c>
-      <c r="G40" s="51" t="s">
-        <v>363</v>
-      </c>
       <c r="H40" s="66" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I40" s="30" t="s">
         <v>140</v>
@@ -9314,22 +9323,22 @@
         <v>32</v>
       </c>
       <c r="C41" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D41" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D41" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E41" s="51" t="s">
+        <v>363</v>
+      </c>
+      <c r="F41" s="54" t="s">
         <v>364</v>
       </c>
-      <c r="F41" s="54" t="s">
+      <c r="G41" s="51" t="s">
         <v>365</v>
       </c>
-      <c r="G41" s="51" t="s">
-        <v>366</v>
-      </c>
       <c r="H41" s="66" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I41" s="30" t="s">
         <v>140</v>
@@ -9341,25 +9350,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="51" t="s">
+        <v>366</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" s="51" t="s">
         <v>367</v>
       </c>
-      <c r="C42" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D42" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E42" s="51" t="s">
+      <c r="F42" s="54" t="s">
+        <v>348</v>
+      </c>
+      <c r="G42" s="51" t="s">
         <v>368</v>
       </c>
-      <c r="F42" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="G42" s="51" t="s">
-        <v>369</v>
-      </c>
       <c r="H42" s="66" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I42" s="30" t="s">
         <v>140</v>
@@ -9371,25 +9380,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C43" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E43" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>351</v>
+      </c>
+      <c r="G43" s="51" t="s">
         <v>370</v>
       </c>
-      <c r="F43" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>371</v>
-      </c>
       <c r="H43" s="66" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I43" s="30" t="s">
         <v>140</v>
@@ -9404,22 +9413,22 @@
         <v>33</v>
       </c>
       <c r="C44" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D44" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D44" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E44" s="51" t="s">
+        <v>371</v>
+      </c>
+      <c r="F44" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="G44" s="51" t="s">
         <v>373</v>
       </c>
-      <c r="G44" s="51" t="s">
-        <v>374</v>
-      </c>
       <c r="H44" s="66" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I44" s="30" t="s">
         <v>140</v>
@@ -9431,25 +9440,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E45" s="51" t="s">
         <v>375</v>
       </c>
-      <c r="C45" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D45" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E45" s="51" t="s">
+      <c r="F45" s="54" t="s">
         <v>376</v>
       </c>
-      <c r="F45" s="54" t="s">
+      <c r="G45" s="51" t="s">
         <v>377</v>
       </c>
-      <c r="G45" s="51" t="s">
-        <v>378</v>
-      </c>
       <c r="H45" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I45" s="30" t="s">
         <v>140</v>
@@ -9461,25 +9470,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D46" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E46" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="F46" s="54" t="s">
         <v>379</v>
       </c>
-      <c r="F46" s="54" t="s">
+      <c r="G46" s="51" t="s">
         <v>380</v>
       </c>
-      <c r="G46" s="51" t="s">
-        <v>381</v>
-      </c>
       <c r="H46" s="66" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I46" s="30" t="s">
         <v>140</v>
@@ -9494,22 +9503,22 @@
         <v>34</v>
       </c>
       <c r="C47" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D47" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D47" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E47" s="51" t="s">
+        <v>381</v>
+      </c>
+      <c r="F47" s="56" t="s">
+        <v>372</v>
+      </c>
+      <c r="G47" s="51" t="s">
         <v>382</v>
       </c>
-      <c r="F47" s="56" t="s">
-        <v>373</v>
-      </c>
-      <c r="G47" s="51" t="s">
-        <v>383</v>
-      </c>
       <c r="H47" s="66" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I47" s="30" t="s">
         <v>140</v>
@@ -9521,25 +9530,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="51" t="s">
+        <v>383</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D48" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="51" t="s">
         <v>384</v>
       </c>
-      <c r="C48" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D48" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E48" s="51" t="s">
+      <c r="F48" s="55" t="s">
         <v>385</v>
       </c>
-      <c r="F48" s="55" t="s">
+      <c r="G48" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="G48" s="51" t="s">
-        <v>387</v>
-      </c>
       <c r="H48" s="66" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I48" s="30" t="s">
         <v>140</v>
@@ -9551,25 +9560,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E49" s="51" t="s">
+        <v>387</v>
+      </c>
+      <c r="F49" s="54" t="s">
         <v>388</v>
       </c>
-      <c r="F49" s="54" t="s">
+      <c r="G49" s="51" t="s">
         <v>389</v>
       </c>
-      <c r="G49" s="51" t="s">
-        <v>390</v>
-      </c>
       <c r="H49" s="64" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I49" s="30" t="s">
         <v>140</v>
@@ -9584,22 +9593,22 @@
         <v>44</v>
       </c>
       <c r="C50" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D50" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D50" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E50" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="F50" s="33" t="s">
         <v>391</v>
       </c>
-      <c r="F50" s="33" t="s">
+      <c r="G50" s="51" t="s">
         <v>392</v>
       </c>
-      <c r="G50" s="51" t="s">
-        <v>393</v>
-      </c>
       <c r="H50" s="66" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I50" s="30" t="s">
         <v>140</v>
@@ -9611,25 +9620,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="51" t="s">
+        <v>393</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D51" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" s="51" t="s">
         <v>394</v>
       </c>
-      <c r="C51" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D51" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E51" s="51" t="s">
+      <c r="F51" s="54" t="s">
+        <v>376</v>
+      </c>
+      <c r="G51" s="51" t="s">
         <v>395</v>
       </c>
-      <c r="F51" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>396</v>
-      </c>
       <c r="H51" s="66" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I51" s="30" t="s">
         <v>140</v>
@@ -9641,25 +9650,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C52" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D52" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E52" s="51" t="s">
+        <v>396</v>
+      </c>
+      <c r="F52" s="54" t="s">
+        <v>379</v>
+      </c>
+      <c r="G52" s="51" t="s">
         <v>397</v>
       </c>
-      <c r="F52" s="54" t="s">
-        <v>380</v>
-      </c>
-      <c r="G52" s="51" t="s">
-        <v>398</v>
-      </c>
       <c r="H52" s="66" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I52" s="30" t="s">
         <v>140</v>
@@ -9674,22 +9683,22 @@
         <v>36</v>
       </c>
       <c r="C53" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D53" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E53" s="51" t="s">
+        <v>398</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="G53" s="51" t="s">
         <v>399</v>
       </c>
-      <c r="F53" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>400</v>
-      </c>
       <c r="H53" s="66" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I53" s="30" t="s">
         <v>140</v>
@@ -9701,25 +9710,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="51" t="s">
+        <v>400</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D54" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E54" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="C54" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D54" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E54" s="51" t="s">
+      <c r="F54" s="54" t="s">
         <v>402</v>
       </c>
-      <c r="F54" s="54" t="s">
+      <c r="G54" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="G54" s="51" t="s">
-        <v>404</v>
-      </c>
       <c r="H54" s="66" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I54" s="30" t="s">
         <v>140</v>
@@ -9731,25 +9740,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D55" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E55" s="51" t="s">
+        <v>404</v>
+      </c>
+      <c r="F55" s="54" t="s">
         <v>405</v>
       </c>
-      <c r="F55" s="54" t="s">
+      <c r="G55" s="51" t="s">
         <v>406</v>
       </c>
-      <c r="G55" s="51" t="s">
-        <v>407</v>
-      </c>
       <c r="H55" s="66" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I55" s="30" t="s">
         <v>140</v>
@@ -9764,22 +9773,22 @@
         <v>37</v>
       </c>
       <c r="C56" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D56" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D56" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E56" s="51" t="s">
+        <v>407</v>
+      </c>
+      <c r="F56" s="54" t="s">
+        <v>372</v>
+      </c>
+      <c r="G56" s="51" t="s">
         <v>408</v>
       </c>
-      <c r="F56" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="G56" s="51" t="s">
-        <v>409</v>
-      </c>
       <c r="H56" s="66" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I56" s="30" t="s">
         <v>140</v>
@@ -9791,25 +9800,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D57" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E57" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="C57" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D57" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E57" s="51" t="s">
+      <c r="F57" s="54" t="s">
         <v>411</v>
       </c>
-      <c r="F57" s="54" t="s">
+      <c r="G57" s="51" t="s">
         <v>412</v>
       </c>
-      <c r="G57" s="51" t="s">
-        <v>413</v>
-      </c>
       <c r="H57" s="66" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I57" s="30" t="s">
         <v>140</v>
@@ -9821,25 +9830,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C58" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D58" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E58" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="F58" s="54" t="s">
         <v>414</v>
       </c>
-      <c r="F58" s="54" t="s">
+      <c r="G58" s="51" t="s">
         <v>415</v>
       </c>
-      <c r="G58" s="51" t="s">
-        <v>416</v>
-      </c>
       <c r="H58" s="64" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I58" s="30" t="s">
         <v>140</v>
@@ -9854,22 +9863,22 @@
         <v>38</v>
       </c>
       <c r="C59" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D59" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E59" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="F59" s="54" t="s">
         <v>417</v>
       </c>
-      <c r="F59" s="54" t="s">
+      <c r="G59" s="51" t="s">
         <v>418</v>
       </c>
-      <c r="G59" s="51" t="s">
-        <v>419</v>
-      </c>
       <c r="H59" s="66" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I59" s="30" t="s">
         <v>140</v>
@@ -9881,25 +9890,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="51" t="s">
+        <v>419</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D60" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="C60" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D60" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E60" s="51" t="s">
+      <c r="F60" s="54" t="s">
+        <v>402</v>
+      </c>
+      <c r="G60" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="F60" s="54" t="s">
-        <v>403</v>
-      </c>
-      <c r="G60" s="51" t="s">
-        <v>422</v>
-      </c>
       <c r="H60" s="64" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I60" s="30" t="s">
         <v>140</v>
@@ -9911,25 +9920,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C61" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E61" s="51" t="s">
+        <v>422</v>
+      </c>
+      <c r="F61" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="G61" s="51" t="s">
         <v>423</v>
       </c>
-      <c r="F61" s="54" t="s">
-        <v>406</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>424</v>
-      </c>
       <c r="H61" s="66" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I61" s="30" t="s">
         <v>140</v>
@@ -9944,22 +9953,22 @@
         <v>39</v>
       </c>
       <c r="C62" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D62" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D62" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E62" s="51" t="s">
+        <v>424</v>
+      </c>
+      <c r="F62" s="54" t="s">
+        <v>372</v>
+      </c>
+      <c r="G62" s="51" t="s">
         <v>425</v>
       </c>
-      <c r="F62" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="G62" s="51" t="s">
-        <v>426</v>
-      </c>
       <c r="H62" s="64" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I62" s="30" t="s">
         <v>140</v>
@@ -9971,25 +9980,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="51" t="s">
+        <v>426</v>
+      </c>
+      <c r="C63" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D63" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="51" t="s">
         <v>427</v>
       </c>
-      <c r="C63" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D63" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E63" s="51" t="s">
+      <c r="F63" s="54" t="s">
         <v>428</v>
       </c>
-      <c r="F63" s="54" t="s">
+      <c r="G63" s="51" t="s">
         <v>429</v>
       </c>
-      <c r="G63" s="51" t="s">
-        <v>430</v>
-      </c>
       <c r="H63" s="66" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I63" s="30" t="s">
         <v>140</v>
@@ -10001,25 +10010,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C64" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D64" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E64" s="51" t="s">
+        <v>430</v>
+      </c>
+      <c r="F64" s="54" t="s">
         <v>431</v>
       </c>
-      <c r="F64" s="54" t="s">
+      <c r="G64" s="51" t="s">
         <v>432</v>
       </c>
-      <c r="G64" s="51" t="s">
-        <v>433</v>
-      </c>
       <c r="H64" s="66" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I64" s="30" t="s">
         <v>140</v>
@@ -10034,22 +10043,22 @@
         <v>40</v>
       </c>
       <c r="C65" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D65" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D65" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E65" s="51" t="s">
+        <v>433</v>
+      </c>
+      <c r="F65" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="G65" s="51" t="s">
         <v>434</v>
       </c>
-      <c r="F65" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>435</v>
-      </c>
       <c r="H65" s="66" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I65" s="30" t="s">
         <v>140</v>
@@ -10064,22 +10073,22 @@
         <v>29</v>
       </c>
       <c r="C66" s="51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D66" s="51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E66" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F66" s="33" t="s">
         <v>436</v>
       </c>
-      <c r="F66" s="33" t="s">
+      <c r="G66" s="51" t="s">
         <v>437</v>
       </c>
-      <c r="G66" s="51" t="s">
-        <v>438</v>
-      </c>
       <c r="H66" s="66" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I66" s="30" t="s">
         <v>140</v>
@@ -10094,22 +10103,22 @@
         <v>29</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D67" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E67" s="51" t="s">
+        <v>438</v>
+      </c>
+      <c r="F67" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="F67" s="33" t="s">
+      <c r="G67" s="51" t="s">
         <v>440</v>
       </c>
-      <c r="G67" s="51" t="s">
-        <v>441</v>
-      </c>
       <c r="H67" s="66" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I67" s="30" t="s">
         <v>140</v>
@@ -10121,25 +10130,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="51" t="s">
+        <v>441</v>
+      </c>
+      <c r="C68" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D68" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" s="51" t="s">
         <v>442</v>
       </c>
-      <c r="C68" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D68" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E68" s="51" t="s">
+      <c r="F68" s="54" t="s">
+        <v>428</v>
+      </c>
+      <c r="G68" s="51" t="s">
         <v>443</v>
       </c>
-      <c r="F68" s="54" t="s">
-        <v>429</v>
-      </c>
-      <c r="G68" s="51" t="s">
-        <v>444</v>
-      </c>
       <c r="H68" s="66" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I68" s="30" t="s">
         <v>140</v>
@@ -10151,25 +10160,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C69" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D69" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E69" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="F69" s="54" t="s">
+        <v>431</v>
+      </c>
+      <c r="G69" s="51" t="s">
         <v>445</v>
       </c>
-      <c r="F69" s="54" t="s">
-        <v>432</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>446</v>
-      </c>
       <c r="H69" s="66" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I69" s="30" t="s">
         <v>140</v>
@@ -10184,22 +10193,22 @@
         <v>43</v>
       </c>
       <c r="C70" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D70" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E70" s="51" t="s">
+        <v>446</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="G70" s="51" t="s">
         <v>447</v>
       </c>
-      <c r="F70" s="33" t="s">
-        <v>373</v>
-      </c>
-      <c r="G70" s="51" t="s">
-        <v>448</v>
-      </c>
       <c r="H70" s="66" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I70" s="30" t="s">
         <v>140</v>
@@ -10211,25 +10220,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="70" t="s">
+        <v>448</v>
+      </c>
+      <c r="C71" s="51" t="s">
         <v>449</v>
       </c>
-      <c r="C71" s="51" t="s">
+      <c r="D71" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" s="51" t="s">
         <v>450</v>
       </c>
-      <c r="D71" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E71" s="51" t="s">
+      <c r="F71" s="54" t="s">
+        <v>472</v>
+      </c>
+      <c r="G71" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="F71" s="54" t="s">
-        <v>473</v>
-      </c>
-      <c r="G71" s="51" t="s">
-        <v>452</v>
-      </c>
       <c r="H71" s="64" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I71" s="30" t="s">
         <v>140</v>
@@ -10241,25 +10250,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="70" t="s">
+        <v>448</v>
+      </c>
+      <c r="C72" s="51" t="s">
         <v>449</v>
       </c>
-      <c r="C72" s="51" t="s">
-        <v>450</v>
-      </c>
       <c r="D72" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E72" s="51" t="s">
+        <v>452</v>
+      </c>
+      <c r="F72" s="54" t="s">
+        <v>473</v>
+      </c>
+      <c r="G72" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="F72" s="54" t="s">
-        <v>474</v>
-      </c>
-      <c r="G72" s="51" t="s">
-        <v>454</v>
-      </c>
       <c r="H72" s="64" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I72" s="30" t="s">
         <v>140</v>
@@ -10274,22 +10283,22 @@
         <v>49</v>
       </c>
       <c r="C73" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="D73" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="D73" s="51" t="s">
-        <v>259</v>
-      </c>
       <c r="E73" s="51" t="s">
+        <v>454</v>
+      </c>
+      <c r="F73" s="54" t="s">
+        <v>474</v>
+      </c>
+      <c r="G73" s="51" t="s">
         <v>455</v>
       </c>
-      <c r="F73" s="54" t="s">
-        <v>475</v>
-      </c>
-      <c r="G73" s="51" t="s">
-        <v>456</v>
-      </c>
       <c r="H73" s="64" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I73" s="30" t="s">
         <v>140</v>
@@ -10301,25 +10310,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="51" t="s">
+        <v>456</v>
+      </c>
+      <c r="C74" s="51" t="s">
+        <v>250</v>
+      </c>
+      <c r="D74" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E74" s="51" t="s">
         <v>457</v>
       </c>
-      <c r="C74" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D74" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="E74" s="51" t="s">
+      <c r="F74" s="54" t="s">
         <v>458</v>
       </c>
-      <c r="F74" s="54" t="s">
+      <c r="G74" s="51" t="s">
         <v>459</v>
       </c>
-      <c r="G74" s="51" t="s">
-        <v>460</v>
-      </c>
       <c r="H74" s="66" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I74" s="30" t="s">
         <v>140</v>
@@ -10331,25 +10340,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D75" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E75" s="51" t="s">
+        <v>460</v>
+      </c>
+      <c r="F75" s="54" t="s">
         <v>461</v>
       </c>
-      <c r="F75" s="54" t="s">
+      <c r="G75" s="51" t="s">
         <v>462</v>
       </c>
-      <c r="G75" s="51" t="s">
-        <v>463</v>
-      </c>
       <c r="H75" s="66" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I75" s="30" t="s">
         <v>140</v>
@@ -10361,25 +10370,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="58" t="s">
+        <v>463</v>
+      </c>
+      <c r="C76" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="D76" s="58" t="s">
+        <v>258</v>
+      </c>
+      <c r="E76" s="58" t="s">
         <v>464</v>
       </c>
-      <c r="C76" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="D76" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="E76" s="58" t="s">
+      <c r="F76" s="59" t="s">
         <v>465</v>
       </c>
-      <c r="F76" s="59" t="s">
+      <c r="G76" s="58" t="s">
         <v>466</v>
       </c>
-      <c r="G76" s="58" t="s">
-        <v>467</v>
-      </c>
       <c r="H76" s="71" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I76" s="68" t="s">
         <v>140</v>
@@ -11330,7 +11339,7 @@
         <v>92</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>96</v>
@@ -11339,7 +11348,7 @@
         <v>97</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>226</v>
@@ -11371,13 +11380,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>471</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>472</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>

--- a/docs/GE2ExcelTestFile.xlsx
+++ b/docs/GE2ExcelTestFile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanmichaelnuera/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D2458DE-DF1A-BD46-98EC-21649627E189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA16F44-1CB8-C44C-9D38-51A5142A189B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GE2 2026 F1 ECBV" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="555">
   <si>
     <t>VARIABLE</t>
   </si>
@@ -1741,13 +1741,22 @@
     <t>Input file not found.</t>
   </si>
   <si>
-    <t>994da7c4d18c65f0dfc5715848fe132556d0f80e705a0e8d620c79939de29e31</t>
-  </si>
-  <si>
-    <t>0abec6611f29374af22889bec468e450657aaa9832886a449fe2d4f937d23295</t>
-  </si>
-  <si>
-    <t>1339927c516401a3dfe3ca7720347c9a4db73f4a20c086ecd315446e6483575e</t>
+    <t>fe2db16b6daf5aefa4b28a411c457632c64264297c59c51017dcc7a4d3996619</t>
+  </si>
+  <si>
+    <t>8a928247c536e01c50724ece39830fe4bbceb25c1923fcf9e2fcc7a5c064822d</t>
+  </si>
+  <si>
+    <t>43581708ae9e6dbe6e50d97e99fb04e3d87c92571d501237b4ffbb96d556dcca</t>
+  </si>
+  <si>
+    <t>This file is not JSON formatted.</t>
+  </si>
+  <si>
+    <t>JSON does not have the expected structure.</t>
+  </si>
+  <si>
+    <t>JSON data has no valid values.</t>
   </si>
 </sst>
 </file>
@@ -2131,7 +2140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2291,9 +2300,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8080,7 +8086,7 @@
     <col min="6" max="6" width="28.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="59" customWidth="1"/>
-    <col min="9" max="9" width="57.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="10.42578125" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -8289,7 +8295,7 @@
         <v>547</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J6" s="62"/>
       <c r="O6" s="47"/>
@@ -8320,7 +8326,7 @@
         <v>480</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J7" s="62"/>
       <c r="O7" s="47"/>
@@ -8351,7 +8357,7 @@
         <v>481</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J8" s="62"/>
     </row>
@@ -8381,7 +8387,7 @@
         <v>482</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J9" s="62"/>
     </row>
@@ -8411,7 +8417,7 @@
         <v>265</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J10" s="62"/>
     </row>
@@ -8441,7 +8447,7 @@
         <v>544</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J11" s="62"/>
     </row>
@@ -8471,7 +8477,7 @@
         <v>475</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J12" s="62"/>
     </row>
@@ -8501,7 +8507,7 @@
         <v>476</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J13" s="62"/>
     </row>
@@ -8531,7 +8537,7 @@
         <v>483</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J14" s="62"/>
     </row>
@@ -8557,11 +8563,11 @@
       <c r="G15" s="65" t="s">
         <v>281</v>
       </c>
-      <c r="H15" s="70" t="s">
+      <c r="H15" s="69" t="s">
         <v>484</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J15" s="62"/>
     </row>
@@ -8591,7 +8597,7 @@
         <v>543</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J16" s="62"/>
     </row>
@@ -8621,7 +8627,7 @@
         <v>485</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J17" s="62"/>
     </row>
@@ -8651,7 +8657,7 @@
         <v>486</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J18" s="62"/>
     </row>
@@ -8681,7 +8687,7 @@
         <v>487</v>
       </c>
       <c r="I19" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J19" s="62"/>
     </row>
@@ -8711,7 +8717,7 @@
         <v>490</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J20" s="62"/>
     </row>
@@ -8741,7 +8747,7 @@
         <v>545</v>
       </c>
       <c r="I21" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J21" s="62"/>
     </row>
@@ -8771,7 +8777,7 @@
         <v>496</v>
       </c>
       <c r="I22" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J22" s="62"/>
     </row>
@@ -8801,7 +8807,7 @@
         <v>500</v>
       </c>
       <c r="I23" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J23" s="62"/>
     </row>
@@ -8831,7 +8837,7 @@
         <v>510</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J24" s="62"/>
     </row>
@@ -8861,7 +8867,7 @@
         <v>513</v>
       </c>
       <c r="I25" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J25" s="62"/>
     </row>
@@ -8891,7 +8897,7 @@
         <v>516</v>
       </c>
       <c r="I26" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J26" s="62"/>
     </row>
@@ -8921,7 +8927,7 @@
         <v>520</v>
       </c>
       <c r="I27" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J27" s="62"/>
     </row>
@@ -8951,7 +8957,7 @@
         <v>521</v>
       </c>
       <c r="I28" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J28" s="62"/>
     </row>
@@ -8981,7 +8987,7 @@
         <v>522</v>
       </c>
       <c r="I29" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J29" s="62"/>
     </row>
@@ -9011,7 +9017,7 @@
         <v>523</v>
       </c>
       <c r="I30" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J30" s="62"/>
     </row>
@@ -9041,7 +9047,7 @@
         <v>525</v>
       </c>
       <c r="I31" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J31" s="62"/>
     </row>
@@ -9071,7 +9077,7 @@
         <v>527</v>
       </c>
       <c r="I32" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J32" s="62"/>
     </row>
@@ -9101,7 +9107,7 @@
         <v>529</v>
       </c>
       <c r="I33" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J33" s="62"/>
     </row>
@@ -9131,7 +9137,7 @@
         <v>532</v>
       </c>
       <c r="I34" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J34" s="62"/>
     </row>
@@ -9161,7 +9167,7 @@
         <v>540</v>
       </c>
       <c r="I35" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J35" s="62"/>
     </row>
@@ -9191,7 +9197,7 @@
         <v>539</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J36" s="62"/>
     </row>
@@ -9221,7 +9227,7 @@
         <v>538</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J37" s="62"/>
     </row>
@@ -9251,7 +9257,7 @@
         <v>537</v>
       </c>
       <c r="I38" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J38" s="62"/>
     </row>
@@ -9281,7 +9287,7 @@
         <v>536</v>
       </c>
       <c r="I39" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J39" s="62"/>
     </row>
@@ -9311,7 +9317,7 @@
         <v>535</v>
       </c>
       <c r="I40" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J40" s="62"/>
     </row>
@@ -9341,7 +9347,7 @@
         <v>534</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J41" s="62"/>
     </row>
@@ -9371,7 +9377,7 @@
         <v>533</v>
       </c>
       <c r="I42" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J42" s="62"/>
     </row>
@@ -9401,7 +9407,7 @@
         <v>531</v>
       </c>
       <c r="I43" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J43" s="62"/>
     </row>
@@ -9431,7 +9437,7 @@
         <v>530</v>
       </c>
       <c r="I44" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J44" s="62"/>
     </row>
@@ -9461,7 +9467,7 @@
         <v>541</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J45" s="62"/>
     </row>
@@ -9491,7 +9497,7 @@
         <v>528</v>
       </c>
       <c r="I46" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J46" s="62"/>
     </row>
@@ -9521,7 +9527,7 @@
         <v>526</v>
       </c>
       <c r="I47" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J47" s="62"/>
     </row>
@@ -9551,7 +9557,7 @@
         <v>546</v>
       </c>
       <c r="I48" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J48" s="62"/>
     </row>
@@ -9581,7 +9587,7 @@
         <v>524</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J49" s="62"/>
     </row>
@@ -9611,7 +9617,7 @@
         <v>542</v>
       </c>
       <c r="I50" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J50" s="62"/>
     </row>
@@ -9641,7 +9647,7 @@
         <v>519</v>
       </c>
       <c r="I51" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J51" s="62"/>
     </row>
@@ -9671,7 +9677,7 @@
         <v>518</v>
       </c>
       <c r="I52" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J52" s="62"/>
     </row>
@@ -9701,7 +9707,7 @@
         <v>517</v>
       </c>
       <c r="I53" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J53" s="62"/>
     </row>
@@ -9731,7 +9737,7 @@
         <v>515</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J54" s="62"/>
     </row>
@@ -9761,7 +9767,7 @@
         <v>514</v>
       </c>
       <c r="I55" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J55" s="62"/>
     </row>
@@ -9791,7 +9797,7 @@
         <v>512</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J56" s="62"/>
     </row>
@@ -9821,7 +9827,7 @@
         <v>511</v>
       </c>
       <c r="I57" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J57" s="62"/>
     </row>
@@ -9851,7 +9857,7 @@
         <v>509</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J58" s="62"/>
     </row>
@@ -9881,7 +9887,7 @@
         <v>508</v>
       </c>
       <c r="I59" s="30" t="s">
-        <v>140</v>
+        <v>553</v>
       </c>
       <c r="J59" s="62"/>
     </row>
@@ -9911,7 +9917,7 @@
         <v>507</v>
       </c>
       <c r="I60" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J60" s="62"/>
     </row>
@@ -9941,7 +9947,7 @@
         <v>506</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J61" s="62"/>
     </row>
@@ -9971,7 +9977,7 @@
         <v>505</v>
       </c>
       <c r="I62" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J62" s="62"/>
     </row>
@@ -10001,7 +10007,7 @@
         <v>504</v>
       </c>
       <c r="I63" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J63" s="62"/>
     </row>
@@ -10031,7 +10037,7 @@
         <v>503</v>
       </c>
       <c r="I64" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J64" s="62"/>
     </row>
@@ -10061,7 +10067,7 @@
         <v>502</v>
       </c>
       <c r="I65" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J65" s="62"/>
     </row>
@@ -10091,7 +10097,7 @@
         <v>501</v>
       </c>
       <c r="I66" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J66" s="62"/>
     </row>
@@ -10121,7 +10127,7 @@
         <v>499</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J67" s="62"/>
     </row>
@@ -10151,7 +10157,7 @@
         <v>498</v>
       </c>
       <c r="I68" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J68" s="62"/>
     </row>
@@ -10181,7 +10187,7 @@
         <v>497</v>
       </c>
       <c r="I69" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J69" s="62"/>
     </row>
@@ -10211,7 +10217,7 @@
         <v>495</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="J70" s="62"/>
     </row>
@@ -10219,7 +10225,7 @@
       <c r="A71" s="63">
         <v>70</v>
       </c>
-      <c r="B71" s="70" t="s">
+      <c r="B71" s="69" t="s">
         <v>448</v>
       </c>
       <c r="C71" s="51" t="s">
@@ -10241,7 +10247,7 @@
         <v>494</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J71" s="62"/>
     </row>
@@ -10249,7 +10255,7 @@
       <c r="A72" s="63">
         <v>71</v>
       </c>
-      <c r="B72" s="70" t="s">
+      <c r="B72" s="69" t="s">
         <v>448</v>
       </c>
       <c r="C72" s="51" t="s">
@@ -10271,7 +10277,7 @@
         <v>493</v>
       </c>
       <c r="I72" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J72" s="62"/>
     </row>
@@ -10279,7 +10285,7 @@
       <c r="A73" s="63">
         <v>72</v>
       </c>
-      <c r="B73" s="70">
+      <c r="B73" s="69">
         <v>49</v>
       </c>
       <c r="C73" s="51" t="s">
@@ -10301,7 +10307,7 @@
         <v>492</v>
       </c>
       <c r="I73" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J73" s="62"/>
     </row>
@@ -10331,7 +10337,7 @@
         <v>491</v>
       </c>
       <c r="I74" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J74" s="62"/>
     </row>
@@ -10361,7 +10367,7 @@
         <v>489</v>
       </c>
       <c r="I75" s="30" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
       <c r="J75" s="62"/>
     </row>
@@ -10387,13 +10393,13 @@
       <c r="G76" s="58" t="s">
         <v>466</v>
       </c>
-      <c r="H76" s="71" t="s">
+      <c r="H76" s="70" t="s">
         <v>488</v>
       </c>
-      <c r="I76" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="J76" s="69"/>
+      <c r="I76" s="30" t="s">
+        <v>554</v>
+      </c>
+      <c r="J76" s="68"/>
     </row>
     <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F77" s="52"/>

--- a/docs/GE2ExcelTestFile.xlsx
+++ b/docs/GE2ExcelTestFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanmichaelnuera/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA16F44-1CB8-C44C-9D38-51A5142A189B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACD896D-E5C7-E64E-AD5D-E3E82A5595A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="583">
   <si>
     <t>VARIABLE</t>
   </si>
@@ -1501,12 +1501,6 @@
     <t>FIELD</t>
   </si>
   <si>
-    <t>1_3_5_6_8_10</t>
-  </si>
-  <si>
-    <t>Full valid path</t>
-  </si>
-  <si>
     <t>Path considering that the input is not found in the file</t>
   </si>
   <si>
@@ -1519,237 +1513,27 @@
     <t xml:space="preserve">Modification of the NAME node using non alpha-numeric character. </t>
   </si>
   <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}}</t>
-  </si>
-  <si>
     <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.pdf"}</t>
   </si>
   <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.docx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>/"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.pdf"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.pdf"/</t>
-  </si>
-  <si>
     <t>{,"FILENAME":"File1357.xlsx"}</t>
   </si>
   <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf""FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf",,"FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf";"FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.jpeg"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf",}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"@@@@@@@@.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":".xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx'}</t>
-  </si>
-  <si>
-    <t>{:"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx""}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsxFile1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID""PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":""}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":'File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":""File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME':"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME"":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME:"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILEPATH":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAMEFILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID""00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf",'FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID"::"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf",""FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf",FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID"."00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf',"FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf"","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf,"FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
     <t>{"PROJECT_ID":,"FILENAME":"File1357.xlsx"}</t>
   </si>
   <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf""00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf",:"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME""FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899aabbccddeeff00112233445566778899aabbccddeeff","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME""File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":'00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.pdf"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME"::"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":""00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME"."File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID':"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID"":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID:"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_NAME":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.pdf"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_IDPROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{'PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{""PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx""File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
     <t>{"PROJECT_ID":"00112233445566778899GgHhIiJjKkLl","FILENAME":"File1357.xlsx"}</t>
   </si>
   <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf""PROJECT_ID":00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx""PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx""FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
     <t>{"PROJECT_ID":"","FILENAME":"File1357.xlsx"}</t>
   </si>
   <si>
-    <t>{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}{"PROJECT_ID":"00112233445566778899AaBbCcDdEeFf","FILENAME":"File1357.xlsx"}</t>
-  </si>
-  <si>
     <t>Input file not found.</t>
   </si>
   <si>
     <t>fe2db16b6daf5aefa4b28a411c457632c64264297c59c51017dcc7a4d3996619</t>
   </si>
   <si>
-    <t>8a928247c536e01c50724ece39830fe4bbceb25c1923fcf9e2fcc7a5c064822d</t>
-  </si>
-  <si>
-    <t>43581708ae9e6dbe6e50d97e99fb04e3d87c92571d501237b4ffbb96d556dcca</t>
-  </si>
-  <si>
     <t>This file is not JSON formatted.</t>
   </si>
   <si>
@@ -1757,6 +1541,306 @@
   </si>
   <si>
     <t>JSON data has no valid values.</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_12_14_15_16_18_19_21_22_23</t>
+  </si>
+  <si>
+    <t>1_2_3_23</t>
+  </si>
+  <si>
+    <t>1_2_4_5_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_7_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_7_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_7_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_7_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_7_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_12_13_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_12_14_13_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_12_14_15_13_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_12_14_15_16_17_23</t>
+  </si>
+  <si>
+    <t>1_2_4_6_8_9_10_11_12_14_15_16_18_19_20_21_22_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1_2_4_6_8_9_10_11_12_14_15_16_18_20_21_22_23</t>
+  </si>
+  <si>
+    <t>structuraltest_1</t>
+  </si>
+  <si>
+    <t>structuraltest_2</t>
+  </si>
+  <si>
+    <t>structuraltest_3</t>
+  </si>
+  <si>
+    <t>structuraltest_4</t>
+  </si>
+  <si>
+    <t>structuraltest_5</t>
+  </si>
+  <si>
+    <t>structuraltest_6</t>
+  </si>
+  <si>
+    <t>structuraltest_7</t>
+  </si>
+  <si>
+    <t>structuraltest_8</t>
+  </si>
+  <si>
+    <t>structuraltest_9</t>
+  </si>
+  <si>
+    <t>structuraltest_10</t>
+  </si>
+  <si>
+    <t>structuraltest_11</t>
+  </si>
+  <si>
+    <t>structuraltest_12</t>
+  </si>
+  <si>
+    <t>structuraltest_13</t>
+  </si>
+  <si>
+    <t>structuraltest_14</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.pdf"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.docx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>/"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.pdf"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx""PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.pdf"/</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b""PROJECT_ID":27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b""FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b",,"FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b";"FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b",}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx""FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{:"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID""PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID""27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID"::"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID"."27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b""27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b",:"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME""FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME""File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME"::"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME"."File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx""File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{""PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{'PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_IDPROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_NAME":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.pdf"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID:"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID"":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID':"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":""27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":'27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.pdf"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b,"FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b"","FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b',"FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b",FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b",""FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b",'FILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAMEFILENAME":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILEPATH":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME:"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME"":"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME':"File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":""File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":'File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":""}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsxFile1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx""}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx'}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":".xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357File1357.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"@@@@@@@@.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.xlsx.xlsx"}</t>
+  </si>
+  <si>
+    <t>{"PROJECT_ID":"27e6024bf39af523a08276bfea060e5b","FILENAME":"File1357.jpeg"}</t>
+  </si>
+  <si>
+    <t>1ffe25ab23b8c47f6d57938791b2fe4c814eb1758f0111e82393d6d4b42d0e09</t>
+  </si>
+  <si>
+    <t>08fc2c8d5e24bd5465c5768619515a99b6c57e76ac2b82d558a899b1d26b3596</t>
+  </si>
+  <si>
+    <t>b2d5b78676845bc972b3f1a66d3250c3fb93041d5d8b0c14908cd7c70af27962</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1850,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1906,6 +1990,13 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF1071E5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2140,7 +2231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2161,7 +2252,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2310,11 +2400,65 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <name val="Times New Roman"/>
@@ -2353,793 +2497,6 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3370,6 +2727,724 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E2F3"/>
@@ -3587,68 +3662,68 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7CA0BFCF-9B7D-40EB-A0CE-1CFB0F2F6856}" name="Table_16" displayName="Table_16" ref="A1:E243" headerRowDxfId="42" totalsRowDxfId="39" headerRowBorderDxfId="41" tableBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7CA0BFCF-9B7D-40EB-A0CE-1CFB0F2F6856}" name="Table_16" displayName="Table_16" ref="A1:E243" headerRowDxfId="43" totalsRowDxfId="40" headerRowBorderDxfId="42" tableBorderDxfId="41">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E148244B-B26E-4371-AE66-0216439F3FF7}" name="VARIABLE" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{910A32DC-17F1-4350-9BFD-B8A55C065A10}" name="RULE" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{A0A6721B-6434-4DC3-84F8-6C2CA9258959}" name="VALID CLASSES" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{6E6B58A9-D7B9-4456-8012-22BA2B0BE1E6}" name="INVALID CLASSES2" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{DFF8E975-1CE2-4FFC-8642-030F82402494}" name="INVALID CLASSES3" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{E148244B-B26E-4371-AE66-0216439F3FF7}" name="VARIABLE" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{910A32DC-17F1-4350-9BFD-B8A55C065A10}" name="RULE" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{A0A6721B-6434-4DC3-84F8-6C2CA9258959}" name="VALID CLASSES" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{6E6B58A9-D7B9-4456-8012-22BA2B0BE1E6}" name="INVALID CLASSES2" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{DFF8E975-1CE2-4FFC-8642-030F82402494}" name="INVALID CLASSES3" dataDxfId="35" totalsRowDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="GE2 20245 F1 CEVL-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{019BC5DD-6C0F-4C0F-A52E-712A69705FF3}" name="Table_27" displayName="Table_27" ref="A1:N28" headerRowDxfId="32" dataDxfId="30" totalsRowDxfId="28" headerRowBorderDxfId="31" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{019BC5DD-6C0F-4C0F-A52E-712A69705FF3}" name="Table_27" displayName="Table_27" ref="A1:N28" headerRowDxfId="33" dataDxfId="31" totalsRowDxfId="29" headerRowBorderDxfId="32" tableBorderDxfId="30">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{2344FBAE-768E-4FE2-8D3D-E6F3117BB3D0}" name="#" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{C67DEDFF-BA10-4E06-97C0-B7D2A850907E}" name="I/O" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{86447A2F-A79B-457A-BA4C-258366C2DA17}" name="TECHNIQUE" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{B2D9E36D-66D1-484D-B0D0-726D21115B6B}" name="VALID/INVALID" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{C54BC7F8-4326-43B3-85D1-944A3F7CB759}" name="ID TEST" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{D447D2A8-D87C-4470-A4AA-DC300CE37D00}" name="DESCRIPTION" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{8FFED957-D0BE-4897-803C-88A57E4282C4}" name="company_cif" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{8AB8E9D9-9404-4ED3-B821-A3010BDEB017}" name="project_achronym" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{F75F0931-7675-4D30-9B6C-3428C2098170}" name="project_description" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{A56FC231-53D6-4466-837C-3F818DCAC0F3}" name="department" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{8CDE433C-629C-4ED8-A0A8-1535D23587CB}" name="date" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{39076076-990F-4FD9-A69C-52063A34F54B}" name="budget" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{F261BB59-FAE4-48A8-9952-780FD7075D9E}" name="RESULT" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{334EA084-6EBA-4455-8832-D2F387CF1E9C}" name="EC,BL COVERED" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{2344FBAE-768E-4FE2-8D3D-E6F3117BB3D0}" name="#" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{C67DEDFF-BA10-4E06-97C0-B7D2A850907E}" name="I/O" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{86447A2F-A79B-457A-BA4C-258366C2DA17}" name="TECHNIQUE" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{B2D9E36D-66D1-484D-B0D0-726D21115B6B}" name="VALID/INVALID" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{C54BC7F8-4326-43B3-85D1-944A3F7CB759}" name="ID TEST" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{D447D2A8-D87C-4470-A4AA-DC300CE37D00}" name="DESCRIPTION" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{8FFED957-D0BE-4897-803C-88A57E4282C4}" name="company_cif" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{8AB8E9D9-9404-4ED3-B821-A3010BDEB017}" name="project_achronym" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{F75F0931-7675-4D30-9B6C-3428C2098170}" name="project_description" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{A56FC231-53D6-4466-837C-3F818DCAC0F3}" name="department" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{8CDE433C-629C-4ED8-A0A8-1535D23587CB}" name="date" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{39076076-990F-4FD9-A69C-52063A34F54B}" name="budget" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{F261BB59-FAE4-48A8-9952-780FD7075D9E}" name="RESULT" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{334EA084-6EBA-4455-8832-D2F387CF1E9C}" name="EC,BL COVERED" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="GE2 2024 F1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C8441356-4D38-4CFF-9AEB-9058F95AD6AE}" name="Table_38" displayName="Table_38" ref="A1:J76" headerRowDxfId="54" dataDxfId="52" totalsRowDxfId="50" headerRowBorderDxfId="53" tableBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C8441356-4D38-4CFF-9AEB-9058F95AD6AE}" name="Table_38" displayName="Table_38" ref="A1:J76" headerRowDxfId="14" dataDxfId="12" totalsRowDxfId="10" headerRowBorderDxfId="13" tableBorderDxfId="11">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{08BE6E71-4892-4166-815C-5EEC5D1BEA07}" name="#" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{1790EE52-3F76-4CA0-A443-D91354538A95}" name="NODE" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{B46C7C60-5F30-4EF8-B4A7-3A0E0CEE272D}" name="TERMINAL  (T) / NO TERMINAL (NT)" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{FE5B11EB-E550-4D56-9C2C-982FEEE412FD}" name="TYPE (DUPLICATION / DELETION / MODIFICATION / VALID)" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{FE3C6543-3D00-413B-ABD0-B0797F99D2FF}" name="ID TEST" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{E67BF4AD-E09C-481D-B97B-B2C558D1A6E9}" name="DESCRIPTION" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{1542EF84-14AD-4C1B-8F6A-4C158ED42433}" name="FILE PATH" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{37DA74C7-0045-408E-9B6B-5C180EF83ACD}" name="FILE CONTENT" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{08BE6E71-4892-4166-815C-5EEC5D1BEA07}" name="#" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{1790EE52-3F76-4CA0-A443-D91354538A95}" name="NODE" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B46C7C60-5F30-4EF8-B4A7-3A0E0CEE272D}" name="TERMINAL  (T) / NO TERMINAL (NT)" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{FE5B11EB-E550-4D56-9C2C-982FEEE412FD}" name="TYPE (DUPLICATION / DELETION / MODIFICATION / VALID)" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{FE3C6543-3D00-413B-ABD0-B0797F99D2FF}" name="ID TEST" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{E67BF4AD-E09C-481D-B97B-B2C558D1A6E9}" name="DESCRIPTION" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{1542EF84-14AD-4C1B-8F6A-4C158ED42433}" name="FILE PATH" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{37DA74C7-0045-408E-9B6B-5C180EF83ACD}" name="FILE CONTENT" dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{33031CEF-B917-456C-95C2-7E84F2367437}" name="EXPECTED RESULT" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{3CAE8DFD-3245-4AAB-BBD7-B9F7EEA36D20}" name="OBSERVATIONS" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{3CAE8DFD-3245-4AAB-BBD7-B9F7EEA36D20}" name="OBSERVATIONS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="GE2 2024 F2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DFBD5C91-677B-43A7-88B4-503E56F4C139}" name="Table_49" displayName="Table_49" ref="A1:G11" headerRowDxfId="13" totalsRowDxfId="10" headerRowBorderDxfId="12" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DFBD5C91-677B-43A7-88B4-503E56F4C139}" name="Table_49" displayName="Table_49" ref="A1:G15" headerRowDxfId="54" totalsRowDxfId="51" headerRowBorderDxfId="53" tableBorderDxfId="52">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{486D65EE-9FBE-446B-B271-9B6259580254}" name="#" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{C9BA298E-0FEC-4D91-9396-21059593F22B}" name="PATH" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{85A96D71-CB8D-44E4-BF01-7ED4CFD816AF}" name="ID TEST" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{8CE08086-ED2D-49C6-AE8C-61829EDA3A7C}" name="DESCRIPTION" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{C90DB361-C62D-4B13-B2DA-A109FB7F155A}" name="FIELD" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{4CA815AE-4693-4DBA-953B-EB0272866CE3}" name="EXPECTED RESULT" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{C60C48E8-4563-4D37-A45E-B910D1760A43}" name="OBSERVATIONS" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{486D65EE-9FBE-446B-B271-9B6259580254}" name="#" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{C9BA298E-0FEC-4D91-9396-21059593F22B}" name="PATH" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{85A96D71-CB8D-44E4-BF01-7ED4CFD816AF}" name="ID TEST" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{8CE08086-ED2D-49C6-AE8C-61829EDA3A7C}" name="DESCRIPTION" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{C90DB361-C62D-4B13-B2DA-A109FB7F155A}" name="FIELD" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{4CA815AE-4693-4DBA-953B-EB0272866CE3}" name="EXPECTED RESULT" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{C60C48E8-4563-4D37-A45E-B910D1760A43}" name="OBSERVATIONS" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="GE2 2024 F3-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3875,7 +3950,7 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1"/>
@@ -3913,7 +3988,7 @@
       <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="18"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -3925,10 +4000,10 @@
       <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
@@ -3984,10 +4059,10 @@
       <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
@@ -4039,7 +4114,7 @@
     </row>
     <row r="13" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="48"/>
+      <c r="B13" s="47"/>
       <c r="C13" s="6" t="s">
         <v>29</v>
       </c>
@@ -4058,7 +4133,7 @@
         <v>32</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="23"/>
+      <c r="F14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
@@ -4212,7 +4287,7 @@
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="48" t="s">
+      <c r="C28" s="47" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="8"/>
@@ -4221,7 +4296,7 @@
     <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="47" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="8"/>
@@ -4230,7 +4305,7 @@
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="47" t="s">
         <v>59</v>
       </c>
       <c r="D30" s="8"/>
@@ -4244,26 +4319,26 @@
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="48" t="s">
+      <c r="A32" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="48" t="s">
+      <c r="D32" s="47" t="s">
         <v>62</v>
       </c>
       <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7"/>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="47" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="8" t="s">
@@ -4273,10 +4348,10 @@
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7"/>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="47" t="s">
         <v>67</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -4287,7 +4362,7 @@
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="48" t="s">
+      <c r="C35" s="47" t="s">
         <v>69</v>
       </c>
       <c r="D35" s="8" t="s">
@@ -4298,7 +4373,7 @@
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="47" t="s">
         <v>71</v>
       </c>
       <c r="D36" s="8" t="s">
@@ -4309,7 +4384,7 @@
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="47" t="s">
         <v>73</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -4318,20 +4393,20 @@
       <c r="E37" s="7"/>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="24"/>
+      <c r="A38" s="23"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="8"/>
       <c r="E38" s="7"/>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="48" t="s">
+      <c r="B39" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="48" t="s">
+      <c r="C39" s="47" t="s">
         <v>76</v>
       </c>
       <c r="D39" s="8" t="s">
@@ -4341,10 +4416,10 @@
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="48" t="s">
+      <c r="C40" s="47" t="s">
         <v>79</v>
       </c>
       <c r="D40" s="8" t="s">
@@ -4355,7 +4430,7 @@
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="48" t="s">
+      <c r="C41" s="47" t="s">
         <v>81</v>
       </c>
       <c r="D41" s="8" t="s">
@@ -4366,7 +4441,7 @@
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="48" t="s">
+      <c r="C42" s="47" t="s">
         <v>83</v>
       </c>
       <c r="D42" s="8" t="s">
@@ -4377,7 +4452,7 @@
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="48" t="s">
+      <c r="C43" s="47" t="s">
         <v>85</v>
       </c>
       <c r="D43" s="8" t="s">
@@ -4388,27 +4463,27 @@
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
-      <c r="C44" s="48" t="s">
+      <c r="C44" s="47" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="7"/>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
+      <c r="A45" s="23"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="8"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="49" t="s">
         <v>90</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -5793,7 +5868,7 @@
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
       <c r="D243" s="8"/>
-      <c r="E243" s="19"/>
+      <c r="E243" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -5810,1291 +5885,1291 @@
   <dimension ref="A1:AD995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="17" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="17" customWidth="1"/>
-    <col min="13" max="13" width="25.7109375" style="17" customWidth="1"/>
-    <col min="14" max="14" width="43.42578125" style="17" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" style="17" customWidth="1"/>
-    <col min="16" max="30" width="10.42578125" style="17" customWidth="1"/>
-    <col min="31" max="16384" width="10.140625" style="17"/>
+    <col min="1" max="1" width="7.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="16" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="16" customWidth="1"/>
+    <col min="13" max="13" width="25.7109375" style="16" customWidth="1"/>
+    <col min="14" max="14" width="43.42578125" style="16" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" style="16" customWidth="1"/>
+    <col min="16" max="30" width="10.42578125" style="16" customWidth="1"/>
+    <col min="31" max="16384" width="10.140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="16" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:30" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
     </row>
     <row r="2" spans="1:30" ht="388" x14ac:dyDescent="0.2">
-      <c r="A2" s="29">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="L2" s="32">
+      <c r="L2" s="31">
         <v>50000</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="N2" s="31" t="s">
+      <c r="N2" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="26"/>
+      <c r="O2" s="25"/>
     </row>
     <row r="3" spans="1:30" ht="85" x14ac:dyDescent="0.2">
-      <c r="A3" s="29">
+      <c r="A3" s="28">
         <v>2</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="28">
         <v>890478</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="28">
         <v>50000.01</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="M3" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="26"/>
+      <c r="O3" s="25"/>
     </row>
     <row r="4" spans="1:30" ht="85" x14ac:dyDescent="0.2">
-      <c r="A4" s="29">
+      <c r="A4" s="28">
         <v>3</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="28">
         <v>999999.99</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="O4" s="26"/>
+      <c r="O4" s="25"/>
     </row>
     <row r="5" spans="1:30" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="29">
+      <c r="A5" s="28">
         <v>4</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5" s="31">
         <v>1000000</v>
       </c>
-      <c r="M5" s="45" t="s">
+      <c r="M5" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="O5" s="26"/>
+      <c r="O5" s="25"/>
     </row>
     <row r="6" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="29">
+      <c r="A6" s="28">
         <v>5</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="K6" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="31">
         <v>50000</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="26"/>
+      <c r="O6" s="25"/>
     </row>
     <row r="7" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="29">
+      <c r="A7" s="28">
         <v>6</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="31">
         <v>75000</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N7" s="31" t="s">
+      <c r="N7" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="O7" s="26"/>
+      <c r="O7" s="25"/>
     </row>
     <row r="8" spans="1:30" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29">
+      <c r="A8" s="28">
         <v>7</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="31">
         <v>75000</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="M8" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="N8" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="25"/>
     </row>
     <row r="9" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>158818501</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="31">
         <v>50000</v>
       </c>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="N9" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="O9" s="26"/>
+      <c r="O9" s="25"/>
     </row>
     <row r="10" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="A10" s="29">
+      <c r="A10" s="28">
         <v>9</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="28">
         <v>158818501</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28">
         <v>123456</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="K10" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="31">
         <v>50000</v>
       </c>
-      <c r="M10" s="29" t="s">
+      <c r="M10" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N10" s="29" t="s">
+      <c r="N10" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="O10" s="26"/>
+      <c r="O10" s="25"/>
     </row>
     <row r="11" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="29">
+      <c r="A11" s="28">
         <v>10</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K11" s="34" t="s">
+      <c r="K11" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="31">
         <v>50000</v>
       </c>
-      <c r="M11" s="29" t="s">
+      <c r="M11" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N11" s="31" t="s">
+      <c r="N11" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="O11" s="26"/>
+      <c r="O11" s="25"/>
     </row>
     <row r="12" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="29">
+      <c r="A12" s="28">
         <v>11</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="H12" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="J12" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K12" s="34" t="s">
+      <c r="K12" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="31">
         <v>50000</v>
       </c>
-      <c r="M12" s="29" t="s">
+      <c r="M12" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N12" s="31" t="s">
+      <c r="N12" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="O12" s="26"/>
-    </row>
-    <row r="13" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="29">
+      <c r="O12" s="25"/>
+    </row>
+    <row r="13" spans="1:30" ht="68" x14ac:dyDescent="0.2">
+      <c r="A13" s="28">
         <v>12</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K13" s="38" t="s">
+      <c r="K13" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="31">
         <v>50000</v>
       </c>
-      <c r="M13" s="29" t="s">
+      <c r="M13" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N13" s="29" t="s">
+      <c r="N13" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="O13" s="26"/>
+      <c r="O13" s="25"/>
     </row>
     <row r="14" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="29">
+      <c r="A14" s="28">
         <v>13</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="H14" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="28">
         <v>12345678976</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="J14" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="K14" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="31">
         <v>50000</v>
       </c>
-      <c r="M14" s="29" t="s">
+      <c r="M14" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N14" s="29" t="s">
+      <c r="N14" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="25"/>
     </row>
     <row r="15" spans="1:30" ht="68" x14ac:dyDescent="0.2">
-      <c r="A15" s="29">
+      <c r="A15" s="28">
         <v>14</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="H15" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="J15" s="29" t="s">
+      <c r="J15" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L15" s="32">
+      <c r="L15" s="31">
         <v>50000</v>
       </c>
-      <c r="M15" s="29" t="s">
+      <c r="M15" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N15" s="31" t="s">
+      <c r="N15" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="O15" s="26"/>
+      <c r="O15" s="25"/>
     </row>
     <row r="16" spans="1:30" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="29">
+      <c r="A16" s="28">
         <v>15</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="29" t="s">
+      <c r="H16" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="J16" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="31">
         <v>50000</v>
       </c>
-      <c r="M16" s="29" t="s">
+      <c r="M16" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N16" s="31" t="s">
+      <c r="N16" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="O16" s="26"/>
+      <c r="O16" s="25"/>
     </row>
     <row r="17" spans="1:15" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29">
+      <c r="A17" s="28">
         <v>16</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="28">
         <v>13579</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K17" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L17" s="32">
+      <c r="L17" s="31">
         <v>50000</v>
       </c>
-      <c r="M17" s="29" t="s">
+      <c r="M17" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N17" s="29" t="s">
+      <c r="N17" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="O17" s="26"/>
+      <c r="O17" s="25"/>
     </row>
     <row r="18" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="29">
+      <c r="A18" s="28">
         <v>17</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="K18" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="L18" s="32">
+      <c r="L18" s="31">
         <v>50000</v>
       </c>
-      <c r="M18" s="29" t="s">
+      <c r="M18" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N18" s="29" t="s">
+      <c r="N18" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="O18" s="26"/>
+      <c r="O18" s="25"/>
     </row>
     <row r="19" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="29">
+      <c r="A19" s="28">
         <v>18</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J19" s="29" t="s">
+      <c r="J19" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="28">
         <v>12122025</v>
       </c>
-      <c r="L19" s="32">
+      <c r="L19" s="31">
         <v>50000</v>
       </c>
-      <c r="M19" s="29" t="s">
+      <c r="M19" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N19" s="29" t="s">
+      <c r="N19" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="O19" s="26"/>
+      <c r="O19" s="25"/>
     </row>
     <row r="20" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A20" s="29">
+      <c r="A20" s="28">
         <v>19</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="H20" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J20" s="29" t="s">
+      <c r="J20" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="33">
         <v>45944</v>
       </c>
-      <c r="L20" s="32">
+      <c r="L20" s="31">
         <v>50000</v>
       </c>
-      <c r="M20" s="29" t="s">
+      <c r="M20" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N20" s="29" t="s">
+      <c r="N20" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="O20" s="26"/>
+      <c r="O20" s="25"/>
     </row>
     <row r="21" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="29">
+      <c r="A21" s="28">
         <v>20</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H21" s="29" t="s">
+      <c r="H21" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I21" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="J21" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K21" s="34" t="s">
+      <c r="K21" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="31">
         <v>50000</v>
       </c>
-      <c r="M21" s="29" t="s">
+      <c r="M21" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N21" s="31" t="s">
+      <c r="N21" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="O21" s="26"/>
+      <c r="O21" s="25"/>
     </row>
     <row r="22" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="29">
+      <c r="A22" s="28">
         <v>21</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="H22" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I22" s="29" t="s">
+      <c r="I22" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J22" s="29" t="s">
+      <c r="J22" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="K22" s="34" t="s">
+      <c r="K22" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="31">
         <v>50000</v>
       </c>
-      <c r="M22" s="29" t="s">
+      <c r="M22" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N22" s="31" t="s">
+      <c r="N22" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="O22" s="26"/>
+      <c r="O22" s="25"/>
     </row>
     <row r="23" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="35">
+      <c r="A23" s="34">
         <v>22</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="29" t="s">
+      <c r="H23" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I23" s="29" t="s">
+      <c r="I23" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J23" s="29" t="s">
+      <c r="J23" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="K23" s="29" t="s">
+      <c r="K23" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="L23" s="32" t="s">
+      <c r="L23" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="M23" s="29" t="s">
+      <c r="M23" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N23" s="29" t="s">
+      <c r="N23" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="O23" s="26"/>
+      <c r="O23" s="25"/>
     </row>
     <row r="24" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="35">
+      <c r="A24" s="34">
         <v>23</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="29" t="s">
+      <c r="H24" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I24" s="29" t="s">
+      <c r="I24" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J24" s="29" t="s">
+      <c r="J24" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K24" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="28">
         <v>49999.99</v>
       </c>
-      <c r="M24" s="29" t="s">
+      <c r="M24" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N24" s="31" t="s">
+      <c r="N24" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="O24" s="26"/>
+      <c r="O24" s="25"/>
     </row>
     <row r="25" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35">
+      <c r="A25" s="34">
         <v>24</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="29" t="s">
+      <c r="H25" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="29" t="s">
+      <c r="I25" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J25" s="29" t="s">
+      <c r="J25" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="28">
         <v>1000000.01</v>
       </c>
-      <c r="M25" s="29" t="s">
+      <c r="M25" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N25" s="31" t="s">
+      <c r="N25" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="O25" s="26"/>
+      <c r="O25" s="25"/>
     </row>
     <row r="26" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="35">
+      <c r="A26" s="34">
         <v>25</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H26" s="29" t="s">
+      <c r="H26" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J26" s="29" t="s">
+      <c r="J26" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="K26" s="29" t="s">
+      <c r="K26" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="28">
         <v>1000000.1</v>
       </c>
-      <c r="M26" s="29" t="s">
+      <c r="M26" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="O26" s="26"/>
+      <c r="O26" s="25"/>
     </row>
     <row r="27" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" s="35">
+      <c r="A27" s="34">
         <v>26</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29" t="s">
+      <c r="C27" s="36"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="H27" s="29" t="s">
+      <c r="H27" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="I27" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="J27" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="31">
         <v>50000</v>
       </c>
-      <c r="M27" s="31" t="s">
+      <c r="M27" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="N27" s="29" t="s">
+      <c r="N27" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="O27" s="26"/>
+      <c r="O27" s="25"/>
     </row>
     <row r="28" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A28" s="35">
+      <c r="A28" s="34">
         <v>27</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="29" t="s">
+      <c r="C28" s="36"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="G28" s="42" t="s">
+      <c r="G28" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="I28" s="36" t="s">
+      <c r="I28" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="J28" s="36" t="s">
+      <c r="J28" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="31">
         <v>50000</v>
       </c>
-      <c r="M28" s="43" t="s">
+      <c r="M28" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="N28" s="44" t="s">
+      <c r="N28" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="O28" s="26"/>
+      <c r="O28" s="25"/>
     </row>
     <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8095,34 +8170,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="56" t="s">
         <v>222</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="57" t="s">
+      <c r="G1" s="56" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="56" t="s">
         <v>226</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="60" t="s">
         <v>227</v>
       </c>
       <c r="K1" s="2"/>
@@ -8145,2264 +8220,2264 @@
       <c r="AB1" s="2"/>
     </row>
     <row r="2" spans="1:28" ht="102" x14ac:dyDescent="0.2">
-      <c r="A2" s="63">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="63" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>231</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="63" t="s">
+        <v>511</v>
+      </c>
+      <c r="I2" s="64" t="s">
+        <v>580</v>
+      </c>
+      <c r="J2" s="61"/>
+      <c r="O2" s="46"/>
+    </row>
+    <row r="3" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="62">
+        <v>2</v>
+      </c>
+      <c r="B3" s="50">
+        <v>47</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="H3" s="63" t="s">
+        <v>512</v>
+      </c>
+      <c r="I3" s="64" t="s">
+        <v>581</v>
+      </c>
+      <c r="J3" s="61"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+    </row>
+    <row r="4" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="62">
+        <v>3</v>
+      </c>
+      <c r="B4" s="50">
+        <v>48</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="H4" s="63" t="s">
+        <v>513</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>582</v>
+      </c>
+      <c r="J4" s="61"/>
+      <c r="O4" s="46"/>
+    </row>
+    <row r="5" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="62">
+        <v>4</v>
+      </c>
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="J5" s="61"/>
+      <c r="O5" s="46"/>
+    </row>
+    <row r="6" spans="1:28" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="62">
+        <v>5</v>
+      </c>
+      <c r="B6" s="50">
+        <v>1</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>248</v>
+      </c>
+      <c r="H6" s="65" t="s">
+        <v>514</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J6" s="61"/>
+      <c r="O6" s="46"/>
+    </row>
+    <row r="7" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="62">
+        <v>6</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>251</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>253</v>
+      </c>
+      <c r="H7" s="65" t="s">
+        <v>515</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J7" s="61"/>
+      <c r="O7" s="46"/>
+    </row>
+    <row r="8" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="62">
+        <v>7</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="H8" s="65" t="s">
+        <v>516</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="62">
+        <v>8</v>
+      </c>
+      <c r="B9" s="50">
+        <v>5</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="H9" s="65" t="s">
+        <v>517</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J9" s="61"/>
+    </row>
+    <row r="10" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="62">
+        <v>9</v>
+      </c>
+      <c r="B10" s="50">
+        <v>3</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="1:28" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="62">
+        <v>10</v>
+      </c>
+      <c r="B11" s="50">
+        <v>3</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="H11" s="63" t="s">
+        <v>518</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="62">
+        <v>11</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="H12" s="63" t="s">
+        <v>519</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J12" s="61"/>
+    </row>
+    <row r="13" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="62">
+        <v>12</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>274</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="H13" s="65" t="s">
+        <v>520</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J13" s="61"/>
+    </row>
+    <row r="14" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="62">
+        <v>13</v>
+      </c>
+      <c r="B14" s="50">
+        <v>9</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>278</v>
+      </c>
+      <c r="H14" s="65" t="s">
+        <v>521</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J14" s="61"/>
+    </row>
+    <row r="15" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="62">
+        <v>14</v>
+      </c>
+      <c r="B15" s="50">
+        <v>6</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>281</v>
+      </c>
+      <c r="H15" s="68" t="s">
+        <v>474</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J15" s="61"/>
+    </row>
+    <row r="16" spans="1:28" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="62">
+        <v>15</v>
+      </c>
+      <c r="B16" s="50">
+        <v>6</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>284</v>
+      </c>
+      <c r="H16" s="65" t="s">
+        <v>522</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J16" s="61"/>
+    </row>
+    <row r="17" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="62">
+        <v>16</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>523</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J17" s="61"/>
+    </row>
+    <row r="18" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="62">
+        <v>17</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>290</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>291</v>
+      </c>
+      <c r="H18" s="65" t="s">
+        <v>524</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J18" s="61"/>
+    </row>
+    <row r="19" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="62">
+        <v>18</v>
+      </c>
+      <c r="B19" s="50">
+        <v>13</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="H19" s="65" t="s">
+        <v>525</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J19" s="61"/>
+    </row>
+    <row r="20" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="62">
+        <v>19</v>
+      </c>
+      <c r="B20" s="50">
+        <v>8</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>297</v>
+      </c>
+      <c r="H20" s="65" t="s">
+        <v>526</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J20" s="61"/>
+    </row>
+    <row r="21" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="62">
+        <v>20</v>
+      </c>
+      <c r="B21" s="50">
+        <v>8</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>299</v>
+      </c>
+      <c r="G21" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>527</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J21" s="61"/>
+    </row>
+    <row r="22" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="62">
+        <v>21</v>
+      </c>
+      <c r="B22" s="50">
+        <v>10</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>303</v>
+      </c>
+      <c r="H22" s="63" t="s">
+        <v>528</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J22" s="61"/>
+    </row>
+    <row r="23" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="62">
+        <v>22</v>
+      </c>
+      <c r="B23" s="50">
+        <v>10</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="G23" s="64" t="s">
+        <v>306</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J23" s="61"/>
+    </row>
+    <row r="24" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="62">
+        <v>23</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>310</v>
+      </c>
+      <c r="H24" s="63" t="s">
+        <v>530</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J24" s="61"/>
+    </row>
+    <row r="25" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="62">
+        <v>24</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>311</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="G25" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="H25" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J25" s="61"/>
+    </row>
+    <row r="26" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="62">
+        <v>25</v>
+      </c>
+      <c r="B26" s="50">
+        <v>20</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>315</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>316</v>
+      </c>
+      <c r="H26" s="65" t="s">
+        <v>532</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J26" s="61"/>
+    </row>
+    <row r="27" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="62">
+        <v>26</v>
+      </c>
+      <c r="B27" s="50">
+        <v>12</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" s="64" t="s">
+        <v>319</v>
+      </c>
+      <c r="H27" s="65" t="s">
+        <v>475</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J27" s="61"/>
+    </row>
+    <row r="28" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="62">
+        <v>27</v>
+      </c>
+      <c r="B28" s="50">
+        <v>12</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="H28" s="65" t="s">
+        <v>533</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J28" s="61"/>
+    </row>
+    <row r="29" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="62">
+        <v>28</v>
+      </c>
+      <c r="B29" s="50">
+        <v>14</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="H29" s="65" t="s">
+        <v>534</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J29" s="61"/>
+    </row>
+    <row r="30" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="62">
+        <v>29</v>
+      </c>
+      <c r="B30" s="50">
+        <v>14</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="H30" s="63" t="s">
+        <v>535</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J30" s="61"/>
+    </row>
+    <row r="31" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="62">
+        <v>30</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="F31" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="H31" s="65" t="s">
+        <v>536</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J31" s="61"/>
+    </row>
+    <row r="32" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="62">
+        <v>31</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="F32" s="63" t="s">
+        <v>334</v>
+      </c>
+      <c r="G32" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="H32" s="63" t="s">
+        <v>537</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J32" s="61"/>
+    </row>
+    <row r="33" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="62">
+        <v>32</v>
+      </c>
+      <c r="B33" s="50">
+        <v>27</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="F33" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="H33" s="65" t="s">
+        <v>538</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J33" s="61"/>
+    </row>
+    <row r="34" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="62">
+        <v>33</v>
+      </c>
+      <c r="B34" s="50">
+        <v>16</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="F34" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="H34" s="65" t="s">
+        <v>539</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J34" s="61"/>
+    </row>
+    <row r="35" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="62">
+        <v>34</v>
+      </c>
+      <c r="B35" s="50">
+        <v>16</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>343</v>
+      </c>
+      <c r="F35" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="G35" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="H35" s="63" t="s">
+        <v>540</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J35" s="61"/>
+    </row>
+    <row r="36" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="62">
+        <v>35</v>
+      </c>
+      <c r="B36" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="F36" s="63" t="s">
+        <v>348</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="H36" s="65" t="s">
+        <v>541</v>
+      </c>
+      <c r="I36" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J36" s="61"/>
+    </row>
+    <row r="37" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="62">
+        <v>36</v>
+      </c>
+      <c r="B37" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="C37" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="H37" s="65" t="s">
+        <v>542</v>
+      </c>
+      <c r="I37" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J37" s="61"/>
+    </row>
+    <row r="38" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="62">
+        <v>37</v>
+      </c>
+      <c r="B38" s="50">
+        <v>31</v>
+      </c>
+      <c r="C38" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>355</v>
+      </c>
+      <c r="H38" s="65" t="s">
+        <v>543</v>
+      </c>
+      <c r="I38" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J38" s="61"/>
+    </row>
+    <row r="39" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="62">
+        <v>38</v>
+      </c>
+      <c r="B39" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" s="65" t="s">
+        <v>544</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="62">
+        <v>39</v>
+      </c>
+      <c r="B40" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="C40" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="G40" s="50" t="s">
+        <v>362</v>
+      </c>
+      <c r="H40" s="65" t="s">
+        <v>545</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="J40" s="61"/>
+    </row>
+    <row r="41" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="62">
+        <v>40</v>
+      </c>
+      <c r="B41" s="52">
+        <v>32</v>
+      </c>
+      <c r="C41" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E41" s="50" t="s">
+        <v>363</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>364</v>
+      </c>
+      <c r="G41" s="50" t="s">
+        <v>365</v>
+      </c>
+      <c r="H41" s="65" t="s">
+        <v>546</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="J41" s="61"/>
+    </row>
+    <row r="42" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="62">
+        <v>41</v>
+      </c>
+      <c r="B42" s="50" t="s">
+        <v>366</v>
+      </c>
+      <c r="C42" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D42" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" s="50" t="s">
+        <v>367</v>
+      </c>
+      <c r="F42" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="G42" s="50" t="s">
+        <v>368</v>
+      </c>
+      <c r="H42" s="65" t="s">
+        <v>547</v>
+      </c>
+      <c r="I42" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J42" s="61"/>
+    </row>
+    <row r="43" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="62">
+        <v>42</v>
+      </c>
+      <c r="B43" s="50" t="s">
+        <v>366</v>
+      </c>
+      <c r="C43" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>369</v>
+      </c>
+      <c r="F43" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="G43" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="H43" s="65" t="s">
+        <v>548</v>
+      </c>
+      <c r="I43" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J43" s="61"/>
+    </row>
+    <row r="44" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="62">
+        <v>43</v>
+      </c>
+      <c r="B44" s="50">
+        <v>33</v>
+      </c>
+      <c r="C44" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>371</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="G44" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="H44" s="65" t="s">
+        <v>549</v>
+      </c>
+      <c r="I44" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J44" s="61"/>
+    </row>
+    <row r="45" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="62">
+        <v>44</v>
+      </c>
+      <c r="B45" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="C45" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>375</v>
+      </c>
+      <c r="F45" s="53" t="s">
+        <v>376</v>
+      </c>
+      <c r="G45" s="50" t="s">
+        <v>377</v>
+      </c>
+      <c r="H45" s="65" t="s">
+        <v>550</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J45" s="61"/>
+    </row>
+    <row r="46" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="62">
+        <v>45</v>
+      </c>
+      <c r="B46" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="C46" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="F46" s="53" t="s">
+        <v>379</v>
+      </c>
+      <c r="G46" s="50" t="s">
+        <v>380</v>
+      </c>
+      <c r="H46" s="65" t="s">
+        <v>551</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J46" s="61"/>
+    </row>
+    <row r="47" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="62">
+        <v>46</v>
+      </c>
+      <c r="B47" s="50">
+        <v>34</v>
+      </c>
+      <c r="C47" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D47" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>381</v>
+      </c>
+      <c r="F47" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="H47" s="65" t="s">
+        <v>552</v>
+      </c>
+      <c r="I47" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J47" s="61"/>
+    </row>
+    <row r="48" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="62">
+        <v>47</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="C48" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D48" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="50" t="s">
+        <v>384</v>
+      </c>
+      <c r="F48" s="54" t="s">
+        <v>385</v>
+      </c>
+      <c r="G48" s="50" t="s">
+        <v>386</v>
+      </c>
+      <c r="H48" s="65" t="s">
         <v>477</v>
       </c>
-      <c r="I2" s="65" t="s">
-        <v>549</v>
-      </c>
-      <c r="J2" s="62"/>
-      <c r="O2" s="47"/>
-    </row>
-    <row r="3" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63">
-        <v>2</v>
-      </c>
-      <c r="B3" s="51">
-        <v>47</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="F3" s="66" t="s">
-        <v>235</v>
-      </c>
-      <c r="G3" s="65" t="s">
-        <v>236</v>
-      </c>
-      <c r="H3" s="64" t="s">
-        <v>478</v>
-      </c>
-      <c r="I3" s="65" t="s">
-        <v>550</v>
-      </c>
-      <c r="J3" s="62"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-    </row>
-    <row r="4" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="63">
-        <v>3</v>
-      </c>
-      <c r="B4" s="51">
+      <c r="I48" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J48" s="61"/>
+    </row>
+    <row r="49" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="62">
         <v>48</v>
       </c>
-      <c r="C4" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F4" s="66" t="s">
-        <v>238</v>
-      </c>
-      <c r="G4" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>479</v>
-      </c>
-      <c r="I4" s="65" t="s">
-        <v>551</v>
-      </c>
-      <c r="J4" s="62"/>
-      <c r="O4" s="47"/>
-    </row>
-    <row r="5" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="63">
-        <v>4</v>
-      </c>
-      <c r="B5" s="51">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D5" s="51" t="s">
+      <c r="B49" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="C49" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D49" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="50" t="s">
+        <v>387</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>388</v>
+      </c>
+      <c r="G49" s="50" t="s">
+        <v>389</v>
+      </c>
+      <c r="H49" s="63" t="s">
+        <v>553</v>
+      </c>
+      <c r="I49" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J49" s="61"/>
+    </row>
+    <row r="50" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="62">
+        <v>49</v>
+      </c>
+      <c r="B50" s="52">
+        <v>44</v>
+      </c>
+      <c r="C50" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D50" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E50" s="50" t="s">
+        <v>390</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="G50" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="H50" s="65" t="s">
+        <v>476</v>
+      </c>
+      <c r="I50" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J50" s="61"/>
+    </row>
+    <row r="51" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="62">
+        <v>50</v>
+      </c>
+      <c r="B51" s="50" t="s">
+        <v>393</v>
+      </c>
+      <c r="C51" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D51" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="E5" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="F5" s="64" t="s">
-        <v>243</v>
-      </c>
-      <c r="G5" s="65" t="s">
-        <v>244</v>
-      </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="30" t="s">
-        <v>548</v>
-      </c>
-      <c r="J5" s="62"/>
-      <c r="O5" s="47"/>
-    </row>
-    <row r="6" spans="1:28" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="63">
-        <v>5</v>
-      </c>
-      <c r="B6" s="51">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="51" t="s">
+      <c r="E51" s="50" t="s">
+        <v>394</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>376</v>
+      </c>
+      <c r="G51" s="50" t="s">
+        <v>395</v>
+      </c>
+      <c r="H51" s="65" t="s">
+        <v>554</v>
+      </c>
+      <c r="I51" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J51" s="61"/>
+    </row>
+    <row r="52" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="62">
+        <v>51</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D52" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="E6" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="F6" s="64" t="s">
-        <v>247</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>248</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>547</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J6" s="62"/>
-      <c r="O6" s="47"/>
-    </row>
-    <row r="7" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="63">
-        <v>6</v>
-      </c>
-      <c r="B7" s="51" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="51" t="s">
+      <c r="E52" s="50" t="s">
+        <v>396</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>379</v>
+      </c>
+      <c r="G52" s="50" t="s">
+        <v>397</v>
+      </c>
+      <c r="H52" s="65" t="s">
+        <v>555</v>
+      </c>
+      <c r="I52" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J52" s="61"/>
+    </row>
+    <row r="53" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="62">
+        <v>52</v>
+      </c>
+      <c r="B53" s="50">
+        <v>36</v>
+      </c>
+      <c r="C53" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E53" s="50" t="s">
+        <v>398</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>399</v>
+      </c>
+      <c r="H53" s="65" t="s">
+        <v>556</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J53" s="61"/>
+    </row>
+    <row r="54" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="62">
+        <v>53</v>
+      </c>
+      <c r="B54" s="50" t="s">
+        <v>400</v>
+      </c>
+      <c r="C54" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D54" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="E7" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="F7" s="64" t="s">
-        <v>252</v>
-      </c>
-      <c r="G7" s="65" t="s">
-        <v>253</v>
-      </c>
-      <c r="H7" s="66" t="s">
+      <c r="E54" s="50" t="s">
+        <v>401</v>
+      </c>
+      <c r="F54" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="G54" s="50" t="s">
+        <v>403</v>
+      </c>
+      <c r="H54" s="65" t="s">
+        <v>557</v>
+      </c>
+      <c r="I54" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="I7" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J7" s="62"/>
-      <c r="O7" s="47"/>
-    </row>
-    <row r="8" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="63">
-        <v>7</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="51" t="s">
+      <c r="J54" s="61"/>
+    </row>
+    <row r="55" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="62">
+        <v>54</v>
+      </c>
+      <c r="B55" s="50" t="s">
+        <v>400</v>
+      </c>
+      <c r="C55" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D55" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="E8" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="G8" s="65" t="s">
-        <v>256</v>
-      </c>
-      <c r="H8" s="66" t="s">
+      <c r="E55" s="50" t="s">
+        <v>404</v>
+      </c>
+      <c r="F55" s="53" t="s">
+        <v>405</v>
+      </c>
+      <c r="G55" s="50" t="s">
+        <v>406</v>
+      </c>
+      <c r="H55" s="65" t="s">
+        <v>558</v>
+      </c>
+      <c r="I55" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J55" s="61"/>
+    </row>
+    <row r="56" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="62">
+        <v>55</v>
+      </c>
+      <c r="B56" s="50">
+        <v>37</v>
+      </c>
+      <c r="C56" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D56" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E56" s="50" t="s">
+        <v>407</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>372</v>
+      </c>
+      <c r="G56" s="50" t="s">
+        <v>408</v>
+      </c>
+      <c r="H56" s="65" t="s">
+        <v>559</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J56" s="61"/>
+    </row>
+    <row r="57" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="62">
+        <v>56</v>
+      </c>
+      <c r="B57" s="50" t="s">
+        <v>409</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>411</v>
+      </c>
+      <c r="G57" s="50" t="s">
+        <v>412</v>
+      </c>
+      <c r="H57" s="65" t="s">
+        <v>560</v>
+      </c>
+      <c r="I57" s="29" t="s">
         <v>481</v>
       </c>
-      <c r="I8" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J8" s="62"/>
-    </row>
-    <row r="9" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="63">
-        <v>8</v>
-      </c>
-      <c r="B9" s="51">
-        <v>5</v>
-      </c>
-      <c r="C9" s="51" t="s">
+      <c r="J57" s="61"/>
+    </row>
+    <row r="58" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="62">
+        <v>57</v>
+      </c>
+      <c r="B58" s="50" t="s">
+        <v>409</v>
+      </c>
+      <c r="C58" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D58" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E58" s="50" t="s">
+        <v>413</v>
+      </c>
+      <c r="F58" s="53" t="s">
+        <v>414</v>
+      </c>
+      <c r="G58" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="H58" s="63" t="s">
+        <v>561</v>
+      </c>
+      <c r="I58" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="J58" s="61"/>
+    </row>
+    <row r="59" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="62">
+        <v>58</v>
+      </c>
+      <c r="B59" s="52">
+        <v>38</v>
+      </c>
+      <c r="C59" s="50" t="s">
         <v>257</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D59" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="E9" s="51" t="s">
-        <v>259</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="H9" s="66" t="s">
+      <c r="E59" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="F59" s="53" t="s">
+        <v>417</v>
+      </c>
+      <c r="G59" s="50" t="s">
+        <v>418</v>
+      </c>
+      <c r="H59" s="65" t="s">
+        <v>562</v>
+      </c>
+      <c r="I59" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="J59" s="61"/>
+    </row>
+    <row r="60" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="62">
+        <v>59</v>
+      </c>
+      <c r="B60" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="C60" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60" s="50" t="s">
+        <v>420</v>
+      </c>
+      <c r="F60" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="G60" s="50" t="s">
+        <v>421</v>
+      </c>
+      <c r="H60" s="63" t="s">
+        <v>563</v>
+      </c>
+      <c r="I60" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J60" s="61"/>
+    </row>
+    <row r="61" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="62">
+        <v>60</v>
+      </c>
+      <c r="B61" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="C61" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D61" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E61" s="50" t="s">
+        <v>422</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>405</v>
+      </c>
+      <c r="G61" s="50" t="s">
+        <v>423</v>
+      </c>
+      <c r="H61" s="65" t="s">
+        <v>564</v>
+      </c>
+      <c r="I61" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J61" s="61"/>
+    </row>
+    <row r="62" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="50">
+        <v>39</v>
+      </c>
+      <c r="C62" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D62" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>424</v>
+      </c>
+      <c r="F62" s="53" t="s">
+        <v>372</v>
+      </c>
+      <c r="G62" s="50" t="s">
+        <v>425</v>
+      </c>
+      <c r="H62" s="63" t="s">
+        <v>565</v>
+      </c>
+      <c r="I62" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J62" s="61"/>
+    </row>
+    <row r="63" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="62">
+        <v>62</v>
+      </c>
+      <c r="B63" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="C63" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D63" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="F63" s="53" t="s">
+        <v>428</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>429</v>
+      </c>
+      <c r="H63" s="65" t="s">
+        <v>566</v>
+      </c>
+      <c r="I63" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J63" s="61"/>
+    </row>
+    <row r="64" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="62">
+        <v>63</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="C64" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D64" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>430</v>
+      </c>
+      <c r="F64" s="53" t="s">
+        <v>431</v>
+      </c>
+      <c r="G64" s="50" t="s">
+        <v>432</v>
+      </c>
+      <c r="H64" s="65" t="s">
+        <v>567</v>
+      </c>
+      <c r="I64" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J64" s="61"/>
+    </row>
+    <row r="65" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="62">
+        <v>64</v>
+      </c>
+      <c r="B65" s="50">
+        <v>40</v>
+      </c>
+      <c r="C65" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D65" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E65" s="50" t="s">
+        <v>433</v>
+      </c>
+      <c r="F65" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>434</v>
+      </c>
+      <c r="H65" s="65" t="s">
+        <v>568</v>
+      </c>
+      <c r="I65" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J65" s="61"/>
+    </row>
+    <row r="66" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="62">
+        <v>65</v>
+      </c>
+      <c r="B66" s="50">
+        <v>29</v>
+      </c>
+      <c r="C66" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="D66" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E66" s="50" t="s">
+        <v>435</v>
+      </c>
+      <c r="F66" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="G66" s="50" t="s">
+        <v>437</v>
+      </c>
+      <c r="H66" s="65" t="s">
+        <v>569</v>
+      </c>
+      <c r="I66" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="I9" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J9" s="62"/>
-    </row>
-    <row r="10" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="63">
-        <v>9</v>
-      </c>
-      <c r="B10" s="51">
-        <v>3</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D10" s="51" t="s">
+      <c r="J66" s="61"/>
+    </row>
+    <row r="67" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="62">
+        <v>66</v>
+      </c>
+      <c r="B67" s="50">
+        <v>29</v>
+      </c>
+      <c r="C67" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E67" s="50" t="s">
+        <v>438</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="G67" s="50" t="s">
+        <v>440</v>
+      </c>
+      <c r="H67" s="65" t="s">
+        <v>570</v>
+      </c>
+      <c r="I67" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J67" s="61"/>
+    </row>
+    <row r="68" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="62">
+        <v>67</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="C68" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D68" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="E10" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" s="64" t="s">
-        <v>263</v>
-      </c>
-      <c r="G10" s="65" t="s">
-        <v>264</v>
-      </c>
-      <c r="H10" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J10" s="62"/>
-    </row>
-    <row r="11" spans="1:28" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="63">
-        <v>10</v>
-      </c>
-      <c r="B11" s="51">
-        <v>3</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D11" s="51" t="s">
+      <c r="E68" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="F68" s="53" t="s">
+        <v>428</v>
+      </c>
+      <c r="G68" s="50" t="s">
+        <v>443</v>
+      </c>
+      <c r="H68" s="65" t="s">
+        <v>571</v>
+      </c>
+      <c r="I68" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J68" s="61"/>
+    </row>
+    <row r="69" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="62">
+        <v>68</v>
+      </c>
+      <c r="B69" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="D69" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="E11" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>267</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>268</v>
-      </c>
-      <c r="H11" s="64" t="s">
-        <v>544</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J11" s="62"/>
-    </row>
-    <row r="12" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="63">
-        <v>11</v>
-      </c>
-      <c r="B12" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" s="51" t="s">
+      <c r="E69" s="50" t="s">
+        <v>444</v>
+      </c>
+      <c r="F69" s="53" t="s">
+        <v>431</v>
+      </c>
+      <c r="G69" s="50" t="s">
+        <v>445</v>
+      </c>
+      <c r="H69" s="65" t="s">
+        <v>572</v>
+      </c>
+      <c r="I69" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J69" s="61"/>
+    </row>
+    <row r="70" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="62">
+        <v>69</v>
+      </c>
+      <c r="B70" s="50">
+        <v>43</v>
+      </c>
+      <c r="C70" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E70" s="50" t="s">
+        <v>446</v>
+      </c>
+      <c r="F70" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="G70" s="50" t="s">
+        <v>447</v>
+      </c>
+      <c r="H70" s="65" t="s">
+        <v>573</v>
+      </c>
+      <c r="I70" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="J70" s="61"/>
+    </row>
+    <row r="71" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="62">
+        <v>70</v>
+      </c>
+      <c r="B71" s="68" t="s">
+        <v>448</v>
+      </c>
+      <c r="C71" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="D71" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E71" s="50" t="s">
+        <v>450</v>
+      </c>
+      <c r="F71" s="53" t="s">
+        <v>470</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>451</v>
+      </c>
+      <c r="H71" s="63" t="s">
+        <v>574</v>
+      </c>
+      <c r="I71" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J71" s="61"/>
+    </row>
+    <row r="72" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="62">
+        <v>71</v>
+      </c>
+      <c r="B72" s="68" t="s">
+        <v>448</v>
+      </c>
+      <c r="C72" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="E72" s="50" t="s">
+        <v>452</v>
+      </c>
+      <c r="F72" s="53" t="s">
+        <v>471</v>
+      </c>
+      <c r="G72" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="H72" s="63" t="s">
+        <v>575</v>
+      </c>
+      <c r="I72" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J72" s="61"/>
+    </row>
+    <row r="73" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="62">
+        <v>72</v>
+      </c>
+      <c r="B73" s="68">
+        <v>49</v>
+      </c>
+      <c r="C73" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="D73" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="E73" s="50" t="s">
+        <v>454</v>
+      </c>
+      <c r="F73" s="53" t="s">
+        <v>472</v>
+      </c>
+      <c r="G73" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="H73" s="63" t="s">
+        <v>576</v>
+      </c>
+      <c r="I73" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J73" s="61"/>
+    </row>
+    <row r="74" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="62">
+        <v>73</v>
+      </c>
+      <c r="B74" s="50" t="s">
+        <v>456</v>
+      </c>
+      <c r="C74" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D74" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="E12" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>271</v>
-      </c>
-      <c r="G12" s="65" t="s">
-        <v>272</v>
-      </c>
-      <c r="H12" s="64" t="s">
-        <v>475</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J12" s="62"/>
-    </row>
-    <row r="13" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63">
-        <v>12</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="C13" s="51" t="s">
+      <c r="E74" s="50" t="s">
+        <v>457</v>
+      </c>
+      <c r="F74" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="G74" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="H74" s="65" t="s">
+        <v>577</v>
+      </c>
+      <c r="I74" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J74" s="61"/>
+    </row>
+    <row r="75" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="62">
+        <v>74</v>
+      </c>
+      <c r="B75" s="50" t="s">
+        <v>456</v>
+      </c>
+      <c r="C75" s="50" t="s">
         <v>250</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D75" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="E13" s="51" t="s">
-        <v>273</v>
-      </c>
-      <c r="F13" s="64" t="s">
-        <v>274</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>275</v>
-      </c>
-      <c r="H13" s="66" t="s">
-        <v>476</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J13" s="62"/>
-    </row>
-    <row r="14" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="63">
-        <v>13</v>
-      </c>
-      <c r="B14" s="51">
-        <v>9</v>
-      </c>
-      <c r="C14" s="51" t="s">
+      <c r="E75" s="50" t="s">
+        <v>460</v>
+      </c>
+      <c r="F75" s="53" t="s">
+        <v>461</v>
+      </c>
+      <c r="G75" s="50" t="s">
+        <v>462</v>
+      </c>
+      <c r="H75" s="65" t="s">
+        <v>578</v>
+      </c>
+      <c r="I75" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J75" s="61"/>
+    </row>
+    <row r="76" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="66">
+        <v>75</v>
+      </c>
+      <c r="B76" s="57" t="s">
+        <v>463</v>
+      </c>
+      <c r="C76" s="57" t="s">
         <v>257</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D76" s="57" t="s">
         <v>258</v>
       </c>
-      <c r="E14" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="G14" s="51" t="s">
-        <v>278</v>
-      </c>
-      <c r="H14" s="66" t="s">
-        <v>483</v>
-      </c>
-      <c r="I14" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J14" s="62"/>
-    </row>
-    <row r="15" spans="1:28" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="63">
-        <v>14</v>
-      </c>
-      <c r="B15" s="51">
-        <v>6</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="F15" s="64" t="s">
-        <v>280</v>
-      </c>
-      <c r="G15" s="65" t="s">
-        <v>281</v>
-      </c>
-      <c r="H15" s="69" t="s">
-        <v>484</v>
-      </c>
-      <c r="I15" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J15" s="62"/>
-    </row>
-    <row r="16" spans="1:28" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="63">
-        <v>15</v>
-      </c>
-      <c r="B16" s="51">
-        <v>6</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="51" t="s">
-        <v>282</v>
-      </c>
-      <c r="F16" s="64" t="s">
-        <v>283</v>
-      </c>
-      <c r="G16" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="H16" s="66" t="s">
-        <v>543</v>
-      </c>
-      <c r="I16" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J16" s="62"/>
-    </row>
-    <row r="17" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63">
-        <v>16</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="F17" s="64" t="s">
-        <v>287</v>
-      </c>
-      <c r="G17" s="65" t="s">
-        <v>288</v>
-      </c>
-      <c r="H17" s="66" t="s">
-        <v>485</v>
-      </c>
-      <c r="I17" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J17" s="62"/>
-    </row>
-    <row r="18" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63">
-        <v>17</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E18" s="51" t="s">
-        <v>289</v>
-      </c>
-      <c r="F18" s="64" t="s">
-        <v>290</v>
-      </c>
-      <c r="G18" s="65" t="s">
-        <v>291</v>
-      </c>
-      <c r="H18" s="66" t="s">
-        <v>486</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J18" s="62"/>
-    </row>
-    <row r="19" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63">
-        <v>18</v>
-      </c>
-      <c r="B19" s="51">
-        <v>13</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>292</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>293</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>294</v>
-      </c>
-      <c r="H19" s="66" t="s">
-        <v>487</v>
-      </c>
-      <c r="I19" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J19" s="62"/>
-    </row>
-    <row r="20" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63">
-        <v>19</v>
-      </c>
-      <c r="B20" s="51">
-        <v>8</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>295</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="G20" s="65" t="s">
-        <v>297</v>
-      </c>
-      <c r="H20" s="66" t="s">
-        <v>490</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J20" s="62"/>
-    </row>
-    <row r="21" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="63">
-        <v>20</v>
-      </c>
-      <c r="B21" s="51">
-        <v>8</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>298</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>299</v>
-      </c>
-      <c r="G21" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="H21" s="66" t="s">
-        <v>545</v>
-      </c>
-      <c r="I21" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J21" s="62"/>
-    </row>
-    <row r="22" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63">
-        <v>21</v>
-      </c>
-      <c r="B22" s="51">
-        <v>10</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D22" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="F22" s="51" t="s">
-        <v>302</v>
-      </c>
-      <c r="G22" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="H22" s="64" t="s">
-        <v>496</v>
-      </c>
-      <c r="I22" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J22" s="62"/>
-    </row>
-    <row r="23" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63">
-        <v>22</v>
-      </c>
-      <c r="B23" s="51">
-        <v>10</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>304</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="G23" s="65" t="s">
-        <v>306</v>
-      </c>
-      <c r="H23" s="66" t="s">
-        <v>500</v>
-      </c>
-      <c r="I23" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J23" s="62"/>
-    </row>
-    <row r="24" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63">
-        <v>23</v>
-      </c>
-      <c r="B24" s="51" t="s">
-        <v>307</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D24" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E24" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="F24" s="64" t="s">
-        <v>309</v>
-      </c>
-      <c r="G24" s="65" t="s">
-        <v>310</v>
-      </c>
-      <c r="H24" s="64" t="s">
-        <v>510</v>
-      </c>
-      <c r="I24" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J24" s="62"/>
-    </row>
-    <row r="25" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="63">
-        <v>24</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>307</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D25" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="64" t="s">
-        <v>312</v>
-      </c>
-      <c r="G25" s="65" t="s">
-        <v>313</v>
-      </c>
-      <c r="H25" s="64" t="s">
-        <v>513</v>
-      </c>
-      <c r="I25" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J25" s="62"/>
-    </row>
-    <row r="26" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63">
-        <v>25</v>
-      </c>
-      <c r="B26" s="51">
-        <v>20</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E26" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="G26" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="H26" s="66" t="s">
-        <v>516</v>
-      </c>
-      <c r="I26" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J26" s="62"/>
-    </row>
-    <row r="27" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="63">
-        <v>26</v>
-      </c>
-      <c r="B27" s="51">
-        <v>12</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>317</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="G27" s="65" t="s">
-        <v>319</v>
-      </c>
-      <c r="H27" s="66" t="s">
-        <v>520</v>
-      </c>
-      <c r="I27" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J27" s="62"/>
-    </row>
-    <row r="28" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A28" s="63">
-        <v>27</v>
-      </c>
-      <c r="B28" s="51">
-        <v>12</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E28" s="51" t="s">
-        <v>320</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="G28" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="H28" s="66" t="s">
-        <v>521</v>
-      </c>
-      <c r="I28" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J28" s="62"/>
-    </row>
-    <row r="29" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="63">
-        <v>28</v>
-      </c>
-      <c r="B29" s="51">
-        <v>14</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="H29" s="66" t="s">
-        <v>522</v>
-      </c>
-      <c r="I29" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J29" s="62"/>
-    </row>
-    <row r="30" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="63">
-        <v>29</v>
-      </c>
-      <c r="B30" s="51">
-        <v>14</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E30" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="F30" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="G30" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="H30" s="64" t="s">
-        <v>523</v>
-      </c>
-      <c r="I30" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J30" s="62"/>
-    </row>
-    <row r="31" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63">
-        <v>30</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>331</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>332</v>
-      </c>
-      <c r="H31" s="66" t="s">
-        <v>525</v>
-      </c>
-      <c r="I31" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J31" s="62"/>
-    </row>
-    <row r="32" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="63">
-        <v>31</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>329</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E32" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="F32" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="G32" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="H32" s="64" t="s">
-        <v>527</v>
-      </c>
-      <c r="I32" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J32" s="62"/>
-    </row>
-    <row r="33" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="63">
-        <v>32</v>
-      </c>
-      <c r="B33" s="51">
-        <v>27</v>
-      </c>
-      <c r="C33" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D33" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E33" s="51" t="s">
-        <v>336</v>
-      </c>
-      <c r="F33" s="64" t="s">
-        <v>337</v>
-      </c>
-      <c r="G33" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="H33" s="66" t="s">
-        <v>529</v>
-      </c>
-      <c r="I33" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J33" s="62"/>
-    </row>
-    <row r="34" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="63">
-        <v>33</v>
-      </c>
-      <c r="B34" s="51">
-        <v>16</v>
-      </c>
-      <c r="C34" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E34" s="51" t="s">
-        <v>339</v>
-      </c>
-      <c r="F34" s="51" t="s">
-        <v>340</v>
-      </c>
-      <c r="G34" s="51" t="s">
-        <v>341</v>
-      </c>
-      <c r="H34" s="66" t="s">
-        <v>532</v>
-      </c>
-      <c r="I34" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J34" s="62"/>
-    </row>
-    <row r="35" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="63">
-        <v>34</v>
-      </c>
-      <c r="B35" s="51">
-        <v>16</v>
-      </c>
-      <c r="C35" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>343</v>
-      </c>
-      <c r="F35" s="51" t="s">
-        <v>344</v>
-      </c>
-      <c r="G35" s="51" t="s">
-        <v>345</v>
-      </c>
-      <c r="H35" s="64" t="s">
-        <v>540</v>
-      </c>
-      <c r="I35" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J35" s="62"/>
-    </row>
-    <row r="36" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="63">
-        <v>35</v>
-      </c>
-      <c r="B36" s="51" t="s">
-        <v>346</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D36" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="51" t="s">
-        <v>347</v>
-      </c>
-      <c r="F36" s="64" t="s">
-        <v>348</v>
-      </c>
-      <c r="G36" s="51" t="s">
-        <v>349</v>
-      </c>
-      <c r="H36" s="66" t="s">
-        <v>539</v>
-      </c>
-      <c r="I36" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J36" s="62"/>
-    </row>
-    <row r="37" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="63">
-        <v>36</v>
-      </c>
-      <c r="B37" s="51" t="s">
-        <v>346</v>
-      </c>
-      <c r="C37" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D37" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>350</v>
-      </c>
-      <c r="F37" s="54" t="s">
-        <v>351</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>352</v>
-      </c>
-      <c r="H37" s="66" t="s">
-        <v>538</v>
-      </c>
-      <c r="I37" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J37" s="62"/>
-    </row>
-    <row r="38" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="63">
-        <v>37</v>
-      </c>
-      <c r="B38" s="51">
-        <v>31</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D38" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E38" s="51" t="s">
-        <v>353</v>
-      </c>
-      <c r="F38" s="51" t="s">
-        <v>354</v>
-      </c>
-      <c r="G38" s="51" t="s">
-        <v>355</v>
-      </c>
-      <c r="H38" s="66" t="s">
-        <v>537</v>
-      </c>
-      <c r="I38" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J38" s="62"/>
-    </row>
-    <row r="39" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63">
-        <v>38</v>
-      </c>
-      <c r="B39" s="51" t="s">
-        <v>356</v>
-      </c>
-      <c r="C39" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>357</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>358</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>359</v>
-      </c>
-      <c r="H39" s="66" t="s">
-        <v>536</v>
-      </c>
-      <c r="I39" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J39" s="62"/>
-    </row>
-    <row r="40" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63">
-        <v>39</v>
-      </c>
-      <c r="B40" s="51" t="s">
-        <v>356</v>
-      </c>
-      <c r="C40" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D40" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="51" t="s">
-        <v>360</v>
-      </c>
-      <c r="F40" s="55" t="s">
-        <v>361</v>
-      </c>
-      <c r="G40" s="51" t="s">
-        <v>362</v>
-      </c>
-      <c r="H40" s="66" t="s">
-        <v>535</v>
-      </c>
-      <c r="I40" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J40" s="62"/>
-    </row>
-    <row r="41" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="63">
-        <v>40</v>
-      </c>
-      <c r="B41" s="53">
-        <v>32</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D41" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>363</v>
-      </c>
-      <c r="F41" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="H41" s="66" t="s">
-        <v>534</v>
-      </c>
-      <c r="I41" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J41" s="62"/>
-    </row>
-    <row r="42" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="63">
-        <v>41</v>
-      </c>
-      <c r="B42" s="51" t="s">
-        <v>366</v>
-      </c>
-      <c r="C42" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D42" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>367</v>
-      </c>
-      <c r="F42" s="54" t="s">
-        <v>348</v>
-      </c>
-      <c r="G42" s="51" t="s">
-        <v>368</v>
-      </c>
-      <c r="H42" s="66" t="s">
-        <v>533</v>
-      </c>
-      <c r="I42" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J42" s="62"/>
-    </row>
-    <row r="43" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="63">
-        <v>42</v>
-      </c>
-      <c r="B43" s="51" t="s">
-        <v>366</v>
-      </c>
-      <c r="C43" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D43" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>369</v>
-      </c>
-      <c r="F43" s="54" t="s">
-        <v>351</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>370</v>
-      </c>
-      <c r="H43" s="66" t="s">
-        <v>531</v>
-      </c>
-      <c r="I43" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J43" s="62"/>
-    </row>
-    <row r="44" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="63">
-        <v>43</v>
-      </c>
-      <c r="B44" s="51">
-        <v>33</v>
-      </c>
-      <c r="C44" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D44" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E44" s="51" t="s">
-        <v>371</v>
-      </c>
-      <c r="F44" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="G44" s="51" t="s">
-        <v>373</v>
-      </c>
-      <c r="H44" s="66" t="s">
-        <v>530</v>
-      </c>
-      <c r="I44" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J44" s="62"/>
-    </row>
-    <row r="45" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="63">
-        <v>44</v>
-      </c>
-      <c r="B45" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C45" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D45" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E45" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="F45" s="54" t="s">
-        <v>376</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>377</v>
-      </c>
-      <c r="H45" s="66" t="s">
-        <v>541</v>
-      </c>
-      <c r="I45" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J45" s="62"/>
-    </row>
-    <row r="46" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="63">
-        <v>45</v>
-      </c>
-      <c r="B46" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C46" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D46" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E46" s="51" t="s">
-        <v>378</v>
-      </c>
-      <c r="F46" s="54" t="s">
-        <v>379</v>
-      </c>
-      <c r="G46" s="51" t="s">
-        <v>380</v>
-      </c>
-      <c r="H46" s="66" t="s">
-        <v>528</v>
-      </c>
-      <c r="I46" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J46" s="62"/>
-    </row>
-    <row r="47" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="63">
-        <v>46</v>
-      </c>
-      <c r="B47" s="51">
-        <v>34</v>
-      </c>
-      <c r="C47" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D47" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>381</v>
-      </c>
-      <c r="F47" s="56" t="s">
-        <v>372</v>
-      </c>
-      <c r="G47" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="H47" s="66" t="s">
-        <v>526</v>
-      </c>
-      <c r="I47" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J47" s="62"/>
-    </row>
-    <row r="48" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="63">
-        <v>47</v>
-      </c>
-      <c r="B48" s="51" t="s">
-        <v>383</v>
-      </c>
-      <c r="C48" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D48" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E48" s="51" t="s">
-        <v>384</v>
-      </c>
-      <c r="F48" s="55" t="s">
-        <v>385</v>
-      </c>
-      <c r="G48" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="H48" s="66" t="s">
-        <v>546</v>
-      </c>
-      <c r="I48" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J48" s="62"/>
-    </row>
-    <row r="49" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="63">
-        <v>48</v>
-      </c>
-      <c r="B49" s="51" t="s">
-        <v>383</v>
-      </c>
-      <c r="C49" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D49" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>387</v>
-      </c>
-      <c r="F49" s="54" t="s">
-        <v>388</v>
-      </c>
-      <c r="G49" s="51" t="s">
-        <v>389</v>
-      </c>
-      <c r="H49" s="64" t="s">
-        <v>524</v>
-      </c>
-      <c r="I49" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J49" s="62"/>
-    </row>
-    <row r="50" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="63">
-        <v>49</v>
-      </c>
-      <c r="B50" s="53">
-        <v>44</v>
-      </c>
-      <c r="C50" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D50" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E50" s="51" t="s">
-        <v>390</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="G50" s="51" t="s">
-        <v>392</v>
-      </c>
-      <c r="H50" s="66" t="s">
-        <v>542</v>
-      </c>
-      <c r="I50" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J50" s="62"/>
-    </row>
-    <row r="51" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="63">
-        <v>50</v>
-      </c>
-      <c r="B51" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="C51" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D51" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>394</v>
-      </c>
-      <c r="F51" s="54" t="s">
-        <v>376</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>395</v>
-      </c>
-      <c r="H51" s="66" t="s">
-        <v>519</v>
-      </c>
-      <c r="I51" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J51" s="62"/>
-    </row>
-    <row r="52" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="63">
-        <v>51</v>
-      </c>
-      <c r="B52" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="C52" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D52" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E52" s="51" t="s">
-        <v>396</v>
-      </c>
-      <c r="F52" s="54" t="s">
-        <v>379</v>
-      </c>
-      <c r="G52" s="51" t="s">
-        <v>397</v>
-      </c>
-      <c r="H52" s="66" t="s">
-        <v>518</v>
-      </c>
-      <c r="I52" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J52" s="62"/>
-    </row>
-    <row r="53" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="63">
-        <v>52</v>
-      </c>
-      <c r="B53" s="51">
-        <v>36</v>
-      </c>
-      <c r="C53" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D53" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E53" s="51" t="s">
-        <v>398</v>
-      </c>
-      <c r="F53" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>399</v>
-      </c>
-      <c r="H53" s="66" t="s">
-        <v>517</v>
-      </c>
-      <c r="I53" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J53" s="62"/>
-    </row>
-    <row r="54" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="63">
-        <v>53</v>
-      </c>
-      <c r="B54" s="51" t="s">
-        <v>400</v>
-      </c>
-      <c r="C54" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D54" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E54" s="51" t="s">
-        <v>401</v>
-      </c>
-      <c r="F54" s="54" t="s">
-        <v>402</v>
-      </c>
-      <c r="G54" s="51" t="s">
-        <v>403</v>
-      </c>
-      <c r="H54" s="66" t="s">
-        <v>515</v>
-      </c>
-      <c r="I54" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J54" s="62"/>
-    </row>
-    <row r="55" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63">
-        <v>54</v>
-      </c>
-      <c r="B55" s="51" t="s">
-        <v>400</v>
-      </c>
-      <c r="C55" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D55" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>404</v>
-      </c>
-      <c r="F55" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="G55" s="51" t="s">
-        <v>406</v>
-      </c>
-      <c r="H55" s="66" t="s">
-        <v>514</v>
-      </c>
-      <c r="I55" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J55" s="62"/>
-    </row>
-    <row r="56" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="63">
-        <v>55</v>
-      </c>
-      <c r="B56" s="51">
-        <v>37</v>
-      </c>
-      <c r="C56" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D56" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E56" s="51" t="s">
-        <v>407</v>
-      </c>
-      <c r="F56" s="54" t="s">
-        <v>372</v>
-      </c>
-      <c r="G56" s="51" t="s">
-        <v>408</v>
-      </c>
-      <c r="H56" s="66" t="s">
-        <v>512</v>
-      </c>
-      <c r="I56" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J56" s="62"/>
-    </row>
-    <row r="57" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="63">
-        <v>56</v>
-      </c>
-      <c r="B57" s="51" t="s">
-        <v>409</v>
-      </c>
-      <c r="C57" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D57" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>410</v>
-      </c>
-      <c r="F57" s="54" t="s">
-        <v>411</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>412</v>
-      </c>
-      <c r="H57" s="66" t="s">
-        <v>511</v>
-      </c>
-      <c r="I57" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J57" s="62"/>
-    </row>
-    <row r="58" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="63">
-        <v>57</v>
-      </c>
-      <c r="B58" s="51" t="s">
-        <v>409</v>
-      </c>
-      <c r="C58" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D58" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E58" s="51" t="s">
-        <v>413</v>
-      </c>
-      <c r="F58" s="54" t="s">
-        <v>414</v>
-      </c>
-      <c r="G58" s="51" t="s">
-        <v>415</v>
-      </c>
-      <c r="H58" s="64" t="s">
-        <v>509</v>
-      </c>
-      <c r="I58" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J58" s="62"/>
-    </row>
-    <row r="59" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="63">
-        <v>58</v>
-      </c>
-      <c r="B59" s="53">
-        <v>38</v>
-      </c>
-      <c r="C59" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D59" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E59" s="51" t="s">
-        <v>416</v>
-      </c>
-      <c r="F59" s="54" t="s">
-        <v>417</v>
-      </c>
-      <c r="G59" s="51" t="s">
-        <v>418</v>
-      </c>
-      <c r="H59" s="66" t="s">
-        <v>508</v>
-      </c>
-      <c r="I59" s="30" t="s">
-        <v>553</v>
-      </c>
-      <c r="J59" s="62"/>
-    </row>
-    <row r="60" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="63">
-        <v>59</v>
-      </c>
-      <c r="B60" s="51" t="s">
-        <v>419</v>
-      </c>
-      <c r="C60" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D60" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E60" s="51" t="s">
-        <v>420</v>
-      </c>
-      <c r="F60" s="54" t="s">
-        <v>402</v>
-      </c>
-      <c r="G60" s="51" t="s">
-        <v>421</v>
-      </c>
-      <c r="H60" s="64" t="s">
-        <v>507</v>
-      </c>
-      <c r="I60" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J60" s="62"/>
-    </row>
-    <row r="61" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="63">
-        <v>60</v>
-      </c>
-      <c r="B61" s="51" t="s">
-        <v>419</v>
-      </c>
-      <c r="C61" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D61" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E61" s="51" t="s">
-        <v>422</v>
-      </c>
-      <c r="F61" s="54" t="s">
-        <v>405</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>423</v>
-      </c>
-      <c r="H61" s="66" t="s">
-        <v>506</v>
-      </c>
-      <c r="I61" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J61" s="62"/>
-    </row>
-    <row r="62" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="63">
-        <v>61</v>
-      </c>
-      <c r="B62" s="51">
-        <v>39</v>
-      </c>
-      <c r="C62" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D62" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E62" s="51" t="s">
-        <v>424</v>
-      </c>
-      <c r="F62" s="54" t="s">
-        <v>372</v>
-      </c>
-      <c r="G62" s="51" t="s">
-        <v>425</v>
-      </c>
-      <c r="H62" s="64" t="s">
-        <v>505</v>
-      </c>
-      <c r="I62" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J62" s="62"/>
-    </row>
-    <row r="63" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="63">
-        <v>62</v>
-      </c>
-      <c r="B63" s="51" t="s">
-        <v>426</v>
-      </c>
-      <c r="C63" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D63" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>427</v>
-      </c>
-      <c r="F63" s="54" t="s">
-        <v>428</v>
-      </c>
-      <c r="G63" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="H63" s="66" t="s">
-        <v>504</v>
-      </c>
-      <c r="I63" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J63" s="62"/>
-    </row>
-    <row r="64" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="63">
-        <v>63</v>
-      </c>
-      <c r="B64" s="51" t="s">
-        <v>426</v>
-      </c>
-      <c r="C64" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D64" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>430</v>
-      </c>
-      <c r="F64" s="54" t="s">
-        <v>431</v>
-      </c>
-      <c r="G64" s="51" t="s">
-        <v>432</v>
-      </c>
-      <c r="H64" s="66" t="s">
-        <v>503</v>
-      </c>
-      <c r="I64" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J64" s="62"/>
-    </row>
-    <row r="65" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="63">
-        <v>64</v>
-      </c>
-      <c r="B65" s="51">
-        <v>40</v>
-      </c>
-      <c r="C65" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D65" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>433</v>
-      </c>
-      <c r="F65" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="H65" s="66" t="s">
-        <v>502</v>
-      </c>
-      <c r="I65" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J65" s="62"/>
-    </row>
-    <row r="66" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="63">
-        <v>65</v>
-      </c>
-      <c r="B66" s="51">
-        <v>29</v>
-      </c>
-      <c r="C66" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="D66" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E66" s="51" t="s">
-        <v>435</v>
-      </c>
-      <c r="F66" s="33" t="s">
-        <v>436</v>
-      </c>
-      <c r="G66" s="51" t="s">
-        <v>437</v>
-      </c>
-      <c r="H66" s="66" t="s">
-        <v>501</v>
-      </c>
-      <c r="I66" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J66" s="62"/>
-    </row>
-    <row r="67" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="63">
-        <v>66</v>
-      </c>
-      <c r="B67" s="51">
-        <v>29</v>
-      </c>
-      <c r="C67" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="D67" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E67" s="51" t="s">
-        <v>438</v>
-      </c>
-      <c r="F67" s="33" t="s">
-        <v>439</v>
-      </c>
-      <c r="G67" s="51" t="s">
-        <v>440</v>
-      </c>
-      <c r="H67" s="66" t="s">
-        <v>499</v>
-      </c>
-      <c r="I67" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J67" s="62"/>
-    </row>
-    <row r="68" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="63">
-        <v>67</v>
-      </c>
-      <c r="B68" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="C68" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D68" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E68" s="51" t="s">
-        <v>442</v>
-      </c>
-      <c r="F68" s="54" t="s">
-        <v>428</v>
-      </c>
-      <c r="G68" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="H68" s="66" t="s">
-        <v>498</v>
-      </c>
-      <c r="I68" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J68" s="62"/>
-    </row>
-    <row r="69" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="63">
-        <v>68</v>
-      </c>
-      <c r="B69" s="51" t="s">
-        <v>441</v>
-      </c>
-      <c r="C69" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D69" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E69" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="F69" s="54" t="s">
-        <v>431</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>445</v>
-      </c>
-      <c r="H69" s="66" t="s">
-        <v>497</v>
-      </c>
-      <c r="I69" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J69" s="62"/>
-    </row>
-    <row r="70" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="63">
-        <v>69</v>
-      </c>
-      <c r="B70" s="51">
-        <v>43</v>
-      </c>
-      <c r="C70" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D70" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E70" s="51" t="s">
-        <v>446</v>
-      </c>
-      <c r="F70" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="G70" s="51" t="s">
-        <v>447</v>
-      </c>
-      <c r="H70" s="66" t="s">
-        <v>495</v>
-      </c>
-      <c r="I70" s="30" t="s">
-        <v>552</v>
-      </c>
-      <c r="J70" s="62"/>
-    </row>
-    <row r="71" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="63">
-        <v>70</v>
-      </c>
-      <c r="B71" s="69" t="s">
-        <v>448</v>
-      </c>
-      <c r="C71" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="D71" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E71" s="51" t="s">
-        <v>450</v>
-      </c>
-      <c r="F71" s="54" t="s">
-        <v>472</v>
-      </c>
-      <c r="G71" s="51" t="s">
-        <v>451</v>
-      </c>
-      <c r="H71" s="64" t="s">
-        <v>494</v>
-      </c>
-      <c r="I71" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J71" s="62"/>
-    </row>
-    <row r="72" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="63">
-        <v>71</v>
-      </c>
-      <c r="B72" s="69" t="s">
-        <v>448</v>
-      </c>
-      <c r="C72" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="D72" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E72" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="F72" s="54" t="s">
-        <v>473</v>
-      </c>
-      <c r="G72" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="H72" s="64" t="s">
-        <v>493</v>
-      </c>
-      <c r="I72" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J72" s="62"/>
-    </row>
-    <row r="73" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="63">
-        <v>72</v>
-      </c>
-      <c r="B73" s="69">
-        <v>49</v>
-      </c>
-      <c r="C73" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="D73" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="E73" s="51" t="s">
-        <v>454</v>
-      </c>
-      <c r="F73" s="54" t="s">
-        <v>474</v>
-      </c>
-      <c r="G73" s="51" t="s">
-        <v>455</v>
-      </c>
-      <c r="H73" s="64" t="s">
-        <v>492</v>
-      </c>
-      <c r="I73" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J73" s="62"/>
-    </row>
-    <row r="74" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="63">
-        <v>73</v>
-      </c>
-      <c r="B74" s="51" t="s">
-        <v>456</v>
-      </c>
-      <c r="C74" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D74" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="E74" s="51" t="s">
-        <v>457</v>
-      </c>
-      <c r="F74" s="54" t="s">
-        <v>458</v>
-      </c>
-      <c r="G74" s="51" t="s">
-        <v>459</v>
-      </c>
-      <c r="H74" s="66" t="s">
-        <v>491</v>
-      </c>
-      <c r="I74" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J74" s="62"/>
-    </row>
-    <row r="75" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="63">
-        <v>74</v>
-      </c>
-      <c r="B75" s="51" t="s">
-        <v>456</v>
-      </c>
-      <c r="C75" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="D75" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E75" s="51" t="s">
-        <v>460</v>
-      </c>
-      <c r="F75" s="54" t="s">
-        <v>461</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>462</v>
-      </c>
-      <c r="H75" s="66" t="s">
-        <v>489</v>
-      </c>
-      <c r="I75" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J75" s="62"/>
-    </row>
-    <row r="76" spans="1:10" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="67">
-        <v>75</v>
-      </c>
-      <c r="B76" s="58" t="s">
-        <v>463</v>
-      </c>
-      <c r="C76" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="D76" s="58" t="s">
-        <v>258</v>
-      </c>
-      <c r="E76" s="58" t="s">
+      <c r="E76" s="57" t="s">
         <v>464</v>
       </c>
-      <c r="F76" s="59" t="s">
+      <c r="F76" s="58" t="s">
         <v>465</v>
       </c>
-      <c r="G76" s="58" t="s">
+      <c r="G76" s="57" t="s">
         <v>466</v>
       </c>
-      <c r="H76" s="70" t="s">
-        <v>488</v>
-      </c>
-      <c r="I76" s="30" t="s">
-        <v>554</v>
-      </c>
-      <c r="J76" s="68"/>
+      <c r="H76" s="69" t="s">
+        <v>579</v>
+      </c>
+      <c r="I76" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="J76" s="67"/>
     </row>
     <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F77" s="52"/>
+      <c r="F77" s="51"/>
     </row>
     <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -11331,35 +11406,35 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.85546875" customWidth="1"/>
+    <col min="6" max="6" width="57.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="25" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>227</v>
       </c>
       <c r="H1" s="2"/>
@@ -11381,143 +11456,267 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="62" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>497</v>
+      </c>
+      <c r="D2" s="71" t="s">
         <v>469</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="10"/>
+      <c r="E2" s="63" t="s">
+        <v>473</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>479</v>
+      </c>
+      <c r="G2" s="72"/>
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="10"/>
+      <c r="B3" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>498</v>
+      </c>
+      <c r="D3" s="71"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
+      <c r="B4" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>499</v>
+      </c>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
+      <c r="B5" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>500</v>
+      </c>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
+      <c r="B6" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>501</v>
+      </c>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
+      <c r="B7" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>502</v>
+      </c>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="72"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
+      <c r="B8" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>503</v>
+      </c>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="10"/>
+      <c r="B9" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>504</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="72"/>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="10"/>
-    </row>
-    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>505</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="72"/>
+    </row>
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="10"/>
-    </row>
-    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B11" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>506</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="72"/>
+    </row>
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="C12" s="71" t="s">
+        <v>507</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="72"/>
+    </row>
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="71" t="s">
+        <v>508</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="72"/>
+    </row>
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="C14" s="71" t="s">
+        <v>509</v>
+      </c>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="72"/>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="C15" s="71" t="s">
+        <v>510</v>
+      </c>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="72"/>
+    </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="70"/>
+    </row>
+    <row r="20" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="70"/>
+    </row>
+    <row r="21" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="70"/>
+    </row>
+    <row r="22" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="70"/>
+    </row>
+    <row r="23" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="70"/>
+    </row>
+    <row r="24" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="70"/>
+    </row>
+    <row r="25" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="70"/>
+    </row>
+    <row r="26" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="70"/>
+    </row>
+    <row r="27" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="70"/>
+    </row>
+    <row r="28" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="70"/>
+    </row>
+    <row r="29" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="70"/>
+    </row>
+    <row r="30" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="70"/>
+    </row>
+    <row r="31" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="70"/>
+    </row>
+    <row r="32" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="70"/>
+    </row>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -12487,6 +12686,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
